--- a/EDT_Edition.xlsx
+++ b/EDT_Edition.xlsx
@@ -805,12 +805,12 @@
     <t>TD-Élément de mécanique-G4</t>
   </si>
   <si>
+    <t>TP-Éléments de mécanique-SG31</t>
+  </si>
+  <si>
     <t>TD-Élément de mécanique-G8</t>
   </si>
   <si>
-    <t>TP-Éléments de mécanique-SG31</t>
-  </si>
-  <si>
     <t>TP-Structure de la matière-SG31</t>
   </si>
   <si>
@@ -1384,12 +1384,12 @@
     <t>TP-Programmation Python-G1A/1B</t>
   </si>
   <si>
+    <t>TP-Ondes et vibrations-G1B/1A</t>
+  </si>
+  <si>
     <t>TP-Électronique fondamentale 01-G2B/2A</t>
   </si>
   <si>
-    <t>TP-Ondes et vibrations-G1B/1A</t>
-  </si>
-  <si>
     <t>TD-Électronique fondamentale 01-G2</t>
   </si>
   <si>
@@ -2689,18 +2689,18 @@
     <t>TP-Ondes et vibrations-G4A/G4B</t>
   </si>
   <si>
+    <t>TD-Électrotechnique fondamentale-G3</t>
+  </si>
+  <si>
+    <t>TP-Électrotechnique fondamentale-G5A/G5B</t>
+  </si>
+  <si>
+    <t>TP-Électrotechnique fondamentale-G4A/G4B</t>
+  </si>
+  <si>
     <t>TP-Électronique fondamentale-G4A/4B/G03</t>
   </si>
   <si>
-    <t>TD-Électrotechnique fondamentale-G3</t>
-  </si>
-  <si>
-    <t>TP-Électrotechnique fondamentale-G5A/G5B</t>
-  </si>
-  <si>
-    <t>TP-Électrotechnique fondamentale-G4A/G4B</t>
-  </si>
-  <si>
     <t>TP-Électronique fondamentale-G2A/2B</t>
   </si>
   <si>
@@ -4297,12 +4297,12 @@
     <t>BENYEKHLEF SOUAD</t>
   </si>
   <si>
+    <t>DR.A.BELASRI</t>
+  </si>
+  <si>
     <t>BOUZIDI ATTOUYA / BENSAAD ZOUAOUI</t>
   </si>
   <si>
-    <t>DR.A.BELASRI</t>
-  </si>
-  <si>
     <t>DR. A. BENKETLAN</t>
   </si>
   <si>
@@ -4783,18 +4783,18 @@
     <t>DRE.K.EZZINE / DR. L MEKHLEF</t>
   </si>
   <si>
+    <t>DR.HAMBI</t>
+  </si>
+  <si>
+    <t>DRE. M. DEKMOUS / DRE. M. HAMBI</t>
+  </si>
+  <si>
+    <t>DRE.M. HAMBI / DR.ZAREB</t>
+  </si>
+  <si>
     <t>BENSAAD ZOUAOUI / PRE.BOUZIDI 33 MME D. BENSIDI AHMED</t>
   </si>
   <si>
-    <t>DR.HAMBI</t>
-  </si>
-  <si>
-    <t>DRE. M. DEKMOUS / DRE. M. HAMBI</t>
-  </si>
-  <si>
-    <t>DRE.M. HAMBI / DR.ZAREB</t>
-  </si>
-  <si>
     <t>TURKI</t>
   </si>
   <si>
@@ -5074,6 +5074,9 @@
     <t>Labo Machine 01</t>
   </si>
   <si>
+    <t>Labo μ-processeurs</t>
+  </si>
+  <si>
     <t>AS04</t>
   </si>
   <si>
@@ -5209,12 +5212,12 @@
     <t>Info 01</t>
   </si>
   <si>
+    <t>Lab B05</t>
+  </si>
+  <si>
     <t>Lab B08</t>
   </si>
   <si>
-    <t>Lab B05</t>
-  </si>
-  <si>
     <t>BS08</t>
   </si>
   <si>
@@ -5257,9 +5260,6 @@
     <t>Labo ELN-P 2</t>
   </si>
   <si>
-    <t>Labo μ-processeurs</t>
-  </si>
-  <si>
     <t>CC-ELN02</t>
   </si>
   <si>
@@ -5374,10 +5374,10 @@
     <t>Lab OV Bloc B5</t>
   </si>
   <si>
+    <t>BS16</t>
+  </si>
+  <si>
     <t>Lab B16 / BS03</t>
-  </si>
-  <si>
-    <t>BS16</t>
   </si>
   <si>
     <t>Salle de TP Systèmes Asservis</t>
@@ -11360,7 +11360,7 @@
         <v>1637</v>
       </c>
       <c r="F211" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="G211" t="s">
         <v>1794</v>
@@ -11412,7 +11412,7 @@
         <v>1637</v>
       </c>
       <c r="F213" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="G213" t="s">
         <v>1794</v>
@@ -11542,7 +11542,7 @@
         <v>1635</v>
       </c>
       <c r="F218" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G218" t="s">
         <v>1795</v>
@@ -11594,7 +11594,7 @@
         <v>1635</v>
       </c>
       <c r="F220" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G220" t="s">
         <v>1795</v>
@@ -11646,7 +11646,7 @@
         <v>1635</v>
       </c>
       <c r="F222" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G222" t="s">
         <v>1795</v>
@@ -11672,7 +11672,7 @@
         <v>1635</v>
       </c>
       <c r="F223" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G223" t="s">
         <v>1795</v>
@@ -11750,7 +11750,7 @@
         <v>1639</v>
       </c>
       <c r="F226" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G226" t="s">
         <v>1795</v>
@@ -11802,7 +11802,7 @@
         <v>1639</v>
       </c>
       <c r="F228" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G228" t="s">
         <v>1795</v>
@@ -11828,7 +11828,7 @@
         <v>1639</v>
       </c>
       <c r="F229" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G229" t="s">
         <v>1795</v>
@@ -11854,7 +11854,7 @@
         <v>1639</v>
       </c>
       <c r="F230" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G230" t="s">
         <v>1795</v>
@@ -12036,7 +12036,7 @@
         <v>1637</v>
       </c>
       <c r="F237" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G237" t="s">
         <v>1795</v>
@@ -12062,7 +12062,7 @@
         <v>1637</v>
       </c>
       <c r="F238" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G238" t="s">
         <v>1795</v>
@@ -12088,7 +12088,7 @@
         <v>1637</v>
       </c>
       <c r="F239" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G239" t="s">
         <v>1795</v>
@@ -12140,7 +12140,7 @@
         <v>1638</v>
       </c>
       <c r="F241" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G241" t="s">
         <v>1795</v>
@@ -12166,7 +12166,7 @@
         <v>1635</v>
       </c>
       <c r="F242" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G242" t="s">
         <v>1796</v>
@@ -12218,7 +12218,7 @@
         <v>1635</v>
       </c>
       <c r="F244" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G244" t="s">
         <v>1796</v>
@@ -12270,7 +12270,7 @@
         <v>1635</v>
       </c>
       <c r="F246" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G246" t="s">
         <v>1796</v>
@@ -12296,7 +12296,7 @@
         <v>1635</v>
       </c>
       <c r="F247" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G247" t="s">
         <v>1796</v>
@@ -12322,7 +12322,7 @@
         <v>1635</v>
       </c>
       <c r="F248" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G248" t="s">
         <v>1796</v>
@@ -12348,7 +12348,7 @@
         <v>1639</v>
       </c>
       <c r="F249" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G249" t="s">
         <v>1796</v>
@@ -12374,7 +12374,7 @@
         <v>1639</v>
       </c>
       <c r="F250" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G250" t="s">
         <v>1796</v>
@@ -12400,7 +12400,7 @@
         <v>1639</v>
       </c>
       <c r="F251" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G251" t="s">
         <v>1796</v>
@@ -12426,7 +12426,7 @@
         <v>1639</v>
       </c>
       <c r="F252" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G252" t="s">
         <v>1796</v>
@@ -12452,7 +12452,7 @@
         <v>1636</v>
       </c>
       <c r="F253" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G253" t="s">
         <v>1796</v>
@@ -12478,7 +12478,7 @@
         <v>1636</v>
       </c>
       <c r="F254" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G254" t="s">
         <v>1796</v>
@@ -12504,7 +12504,7 @@
         <v>1636</v>
       </c>
       <c r="F255" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G255" t="s">
         <v>1796</v>
@@ -12530,7 +12530,7 @@
         <v>1636</v>
       </c>
       <c r="F256" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G256" t="s">
         <v>1796</v>
@@ -12556,7 +12556,7 @@
         <v>1636</v>
       </c>
       <c r="F257" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G257" t="s">
         <v>1796</v>
@@ -12582,7 +12582,7 @@
         <v>1637</v>
       </c>
       <c r="F258" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G258" t="s">
         <v>1796</v>
@@ -12608,7 +12608,7 @@
         <v>1637</v>
       </c>
       <c r="F259" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G259" t="s">
         <v>1796</v>
@@ -12634,7 +12634,7 @@
         <v>1637</v>
       </c>
       <c r="F260" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G260" t="s">
         <v>1796</v>
@@ -12660,7 +12660,7 @@
         <v>1637</v>
       </c>
       <c r="F261" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G261" t="s">
         <v>1796</v>
@@ -12686,7 +12686,7 @@
         <v>1638</v>
       </c>
       <c r="F262" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G262" t="s">
         <v>1796</v>
@@ -12712,7 +12712,7 @@
         <v>1638</v>
       </c>
       <c r="F263" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G263" t="s">
         <v>1796</v>
@@ -12738,7 +12738,7 @@
         <v>1638</v>
       </c>
       <c r="F264" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G264" t="s">
         <v>1796</v>
@@ -12764,7 +12764,7 @@
         <v>1638</v>
       </c>
       <c r="F265" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G265" t="s">
         <v>1796</v>
@@ -12790,7 +12790,7 @@
         <v>1638</v>
       </c>
       <c r="F266" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G266" t="s">
         <v>1796</v>
@@ -12842,7 +12842,7 @@
         <v>1635</v>
       </c>
       <c r="F268" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G268" t="s">
         <v>1797</v>
@@ -12920,7 +12920,7 @@
         <v>1639</v>
       </c>
       <c r="F271" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G271" t="s">
         <v>1797</v>
@@ -12946,7 +12946,7 @@
         <v>1639</v>
       </c>
       <c r="F272" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G272" t="s">
         <v>1797</v>
@@ -12972,7 +12972,7 @@
         <v>1639</v>
       </c>
       <c r="F273" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G273" t="s">
         <v>1797</v>
@@ -12998,7 +12998,7 @@
         <v>1639</v>
       </c>
       <c r="F274" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G274" t="s">
         <v>1797</v>
@@ -13024,7 +13024,7 @@
         <v>1636</v>
       </c>
       <c r="F275" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G275" t="s">
         <v>1797</v>
@@ -13050,7 +13050,7 @@
         <v>1636</v>
       </c>
       <c r="F276" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G276" t="s">
         <v>1797</v>
@@ -13076,7 +13076,7 @@
         <v>1636</v>
       </c>
       <c r="F277" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G277" t="s">
         <v>1797</v>
@@ -13102,7 +13102,7 @@
         <v>1636</v>
       </c>
       <c r="F278" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G278" t="s">
         <v>1797</v>
@@ -13128,7 +13128,7 @@
         <v>1636</v>
       </c>
       <c r="F279" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G279" t="s">
         <v>1797</v>
@@ -13154,7 +13154,7 @@
         <v>1636</v>
       </c>
       <c r="F280" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G280" t="s">
         <v>1797</v>
@@ -13206,7 +13206,7 @@
         <v>1637</v>
       </c>
       <c r="F282" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G282" t="s">
         <v>1797</v>
@@ -13232,7 +13232,7 @@
         <v>1637</v>
       </c>
       <c r="F283" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G283" t="s">
         <v>1797</v>
@@ -13310,7 +13310,7 @@
         <v>1638</v>
       </c>
       <c r="F286" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G286" t="s">
         <v>1797</v>
@@ -13336,7 +13336,7 @@
         <v>1638</v>
       </c>
       <c r="F287" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G287" t="s">
         <v>1797</v>
@@ -13362,7 +13362,7 @@
         <v>1638</v>
       </c>
       <c r="F288" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G288" t="s">
         <v>1797</v>
@@ -13388,7 +13388,7 @@
         <v>1638</v>
       </c>
       <c r="F289" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G289" t="s">
         <v>1797</v>
@@ -13414,7 +13414,7 @@
         <v>1638</v>
       </c>
       <c r="F290" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G290" t="s">
         <v>1797</v>
@@ -13726,7 +13726,7 @@
         <v>1636</v>
       </c>
       <c r="F302" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G302" t="s">
         <v>1798</v>
@@ -13752,7 +13752,7 @@
         <v>1636</v>
       </c>
       <c r="F303" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G303" t="s">
         <v>1798</v>
@@ -13778,7 +13778,7 @@
         <v>1636</v>
       </c>
       <c r="F304" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G304" t="s">
         <v>1798</v>
@@ -13934,7 +13934,7 @@
         <v>1638</v>
       </c>
       <c r="F310" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G310" t="s">
         <v>1798</v>
@@ -13960,7 +13960,7 @@
         <v>1638</v>
       </c>
       <c r="F311" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G311" t="s">
         <v>1798</v>
@@ -14220,7 +14220,7 @@
         <v>1639</v>
       </c>
       <c r="F321" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G321" t="s">
         <v>1799</v>
@@ -14272,7 +14272,7 @@
         <v>1636</v>
       </c>
       <c r="F323" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G323" t="s">
         <v>1799</v>
@@ -14324,7 +14324,7 @@
         <v>1636</v>
       </c>
       <c r="F325" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="G325" t="s">
         <v>1799</v>
@@ -14376,7 +14376,7 @@
         <v>1637</v>
       </c>
       <c r="F327" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G327" t="s">
         <v>1799</v>
@@ -14402,7 +14402,7 @@
         <v>1637</v>
       </c>
       <c r="F328" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="G328" t="s">
         <v>1799</v>
@@ -14480,7 +14480,7 @@
         <v>1637</v>
       </c>
       <c r="F331" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G331" t="s">
         <v>1799</v>
@@ -14532,7 +14532,7 @@
         <v>1638</v>
       </c>
       <c r="F333" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G333" t="s">
         <v>1799</v>
@@ -14584,7 +14584,7 @@
         <v>1635</v>
       </c>
       <c r="F335" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G335" t="s">
         <v>1800</v>
@@ -14636,7 +14636,7 @@
         <v>1635</v>
       </c>
       <c r="F337" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G337" t="s">
         <v>1800</v>
@@ -14766,7 +14766,7 @@
         <v>1635</v>
       </c>
       <c r="F342" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G342" t="s">
         <v>1800</v>
@@ -14844,7 +14844,7 @@
         <v>1635</v>
       </c>
       <c r="F345" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G345" t="s">
         <v>1800</v>
@@ -14922,7 +14922,7 @@
         <v>1635</v>
       </c>
       <c r="F348" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G348" t="s">
         <v>1800</v>
@@ -15026,7 +15026,7 @@
         <v>1635</v>
       </c>
       <c r="F352" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G352" t="s">
         <v>1800</v>
@@ -15078,7 +15078,7 @@
         <v>1635</v>
       </c>
       <c r="F354" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G354" t="s">
         <v>1800</v>
@@ -15130,7 +15130,7 @@
         <v>1635</v>
       </c>
       <c r="F356" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G356" t="s">
         <v>1800</v>
@@ -15156,7 +15156,7 @@
         <v>1639</v>
       </c>
       <c r="F357" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G357" t="s">
         <v>1800</v>
@@ -15248,10 +15248,10 @@
         <v>263</v>
       </c>
       <c r="B361" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
       <c r="C361" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D361" t="s">
         <v>1613</v>
@@ -15260,7 +15260,7 @@
         <v>1639</v>
       </c>
       <c r="F361" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="G361" t="s">
         <v>1800</v>
@@ -15274,10 +15274,10 @@
         <v>264</v>
       </c>
       <c r="B362" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="C362" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D362" t="s">
         <v>1613</v>
@@ -15286,7 +15286,7 @@
         <v>1639</v>
       </c>
       <c r="F362" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="G362" t="s">
         <v>1800</v>
@@ -15323,13 +15323,13 @@
     </row>
     <row r="364" spans="1:8">
       <c r="A364" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B364" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
       <c r="C364" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D364" t="s">
         <v>1614</v>
@@ -15338,7 +15338,7 @@
         <v>1639</v>
       </c>
       <c r="F364" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="G364" t="s">
         <v>1800</v>
@@ -15349,13 +15349,13 @@
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B365" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="C365" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D365" t="s">
         <v>1614</v>
@@ -15364,7 +15364,7 @@
         <v>1639</v>
       </c>
       <c r="F365" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="G365" t="s">
         <v>1800</v>
@@ -15390,7 +15390,7 @@
         <v>1639</v>
       </c>
       <c r="F366" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G366" t="s">
         <v>1800</v>
@@ -15416,7 +15416,7 @@
         <v>1639</v>
       </c>
       <c r="F367" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G367" t="s">
         <v>1800</v>
@@ -15520,7 +15520,7 @@
         <v>1636</v>
       </c>
       <c r="F371" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G371" t="s">
         <v>1800</v>
@@ -15676,7 +15676,7 @@
         <v>1636</v>
       </c>
       <c r="F377" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G377" t="s">
         <v>1800</v>
@@ -15806,7 +15806,7 @@
         <v>1636</v>
       </c>
       <c r="F382" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G382" t="s">
         <v>1800</v>
@@ -15962,7 +15962,7 @@
         <v>1636</v>
       </c>
       <c r="F388" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G388" t="s">
         <v>1800</v>
@@ -16326,7 +16326,7 @@
         <v>1637</v>
       </c>
       <c r="F402" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G402" t="s">
         <v>1800</v>
@@ -16456,7 +16456,7 @@
         <v>1637</v>
       </c>
       <c r="F407" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G407" t="s">
         <v>1800</v>
@@ -16690,7 +16690,7 @@
         <v>1637</v>
       </c>
       <c r="F416" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G416" t="s">
         <v>1800</v>
@@ -16846,7 +16846,7 @@
         <v>1637</v>
       </c>
       <c r="F422" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G422" t="s">
         <v>1800</v>
@@ -16872,7 +16872,7 @@
         <v>1637</v>
       </c>
       <c r="F423" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G423" t="s">
         <v>1800</v>
@@ -16898,7 +16898,7 @@
         <v>1637</v>
       </c>
       <c r="F424" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G424" t="s">
         <v>1800</v>
@@ -16924,7 +16924,7 @@
         <v>1637</v>
       </c>
       <c r="F425" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G425" t="s">
         <v>1800</v>
@@ -16950,7 +16950,7 @@
         <v>1637</v>
       </c>
       <c r="F426" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G426" t="s">
         <v>1800</v>
@@ -16976,7 +16976,7 @@
         <v>1638</v>
       </c>
       <c r="F427" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G427" t="s">
         <v>1800</v>
@@ -17106,7 +17106,7 @@
         <v>1638</v>
       </c>
       <c r="F432" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G432" t="s">
         <v>1800</v>
@@ -17236,7 +17236,7 @@
         <v>1638</v>
       </c>
       <c r="F437" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G437" t="s">
         <v>1800</v>
@@ -17314,7 +17314,7 @@
         <v>1638</v>
       </c>
       <c r="F440" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G440" t="s">
         <v>1800</v>
@@ -17392,7 +17392,7 @@
         <v>1638</v>
       </c>
       <c r="F443" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G443" t="s">
         <v>1800</v>
@@ -17522,7 +17522,7 @@
         <v>1638</v>
       </c>
       <c r="F448" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G448" t="s">
         <v>1800</v>
@@ -17860,7 +17860,7 @@
         <v>1637</v>
       </c>
       <c r="F461" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="G461" t="s">
         <v>1801</v>
@@ -17886,7 +17886,7 @@
         <v>1637</v>
       </c>
       <c r="F462" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G462" t="s">
         <v>1801</v>
@@ -17912,7 +17912,7 @@
         <v>1637</v>
       </c>
       <c r="F463" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="G463" t="s">
         <v>1801</v>
@@ -18094,7 +18094,7 @@
         <v>1638</v>
       </c>
       <c r="F470" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G470" t="s">
         <v>1801</v>
@@ -18198,7 +18198,7 @@
         <v>1635</v>
       </c>
       <c r="F474" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G474" t="s">
         <v>1802</v>
@@ -18224,7 +18224,7 @@
         <v>1635</v>
       </c>
       <c r="F475" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G475" t="s">
         <v>1802</v>
@@ -18328,7 +18328,7 @@
         <v>1639</v>
       </c>
       <c r="F479" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="G479" t="s">
         <v>1802</v>
@@ -18354,7 +18354,7 @@
         <v>1639</v>
       </c>
       <c r="F480" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G480" t="s">
         <v>1802</v>
@@ -18735,7 +18735,7 @@
         <v>1031</v>
       </c>
       <c r="C495" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D495" t="s">
         <v>1612</v>
@@ -18744,7 +18744,7 @@
         <v>1635</v>
       </c>
       <c r="F495" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G495" t="s">
         <v>1803</v>
@@ -18761,7 +18761,7 @@
         <v>1031</v>
       </c>
       <c r="C496" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D496" t="s">
         <v>1612</v>
@@ -18770,7 +18770,7 @@
         <v>1635</v>
       </c>
       <c r="F496" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G496" t="s">
         <v>1803</v>
@@ -18796,7 +18796,7 @@
         <v>1635</v>
       </c>
       <c r="F497" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G497" t="s">
         <v>1803</v>
@@ -18822,7 +18822,7 @@
         <v>1635</v>
       </c>
       <c r="F498" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G498" t="s">
         <v>1803</v>
@@ -18848,7 +18848,7 @@
         <v>1635</v>
       </c>
       <c r="F499" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G499" t="s">
         <v>1803</v>
@@ -18874,7 +18874,7 @@
         <v>1635</v>
       </c>
       <c r="F500" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G500" t="s">
         <v>1803</v>
@@ -19108,7 +19108,7 @@
         <v>1636</v>
       </c>
       <c r="F509" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G509" t="s">
         <v>1803</v>
@@ -19134,7 +19134,7 @@
         <v>1636</v>
       </c>
       <c r="F510" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G510" t="s">
         <v>1803</v>
@@ -19160,7 +19160,7 @@
         <v>1636</v>
       </c>
       <c r="F511" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G511" t="s">
         <v>1803</v>
@@ -19290,7 +19290,7 @@
         <v>1636</v>
       </c>
       <c r="F516" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G516" t="s">
         <v>1803</v>
@@ -19342,7 +19342,7 @@
         <v>1637</v>
       </c>
       <c r="F518" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G518" t="s">
         <v>1803</v>
@@ -19368,7 +19368,7 @@
         <v>1637</v>
       </c>
       <c r="F519" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G519" t="s">
         <v>1803</v>
@@ -19385,7 +19385,7 @@
         <v>1031</v>
       </c>
       <c r="C520" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D520" t="s">
         <v>1615</v>
@@ -19394,7 +19394,7 @@
         <v>1637</v>
       </c>
       <c r="F520" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G520" t="s">
         <v>1803</v>
@@ -19411,7 +19411,7 @@
         <v>1031</v>
       </c>
       <c r="C521" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D521" t="s">
         <v>1615</v>
@@ -19420,7 +19420,7 @@
         <v>1637</v>
       </c>
       <c r="F521" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G521" t="s">
         <v>1803</v>
@@ -19446,7 +19446,7 @@
         <v>1637</v>
       </c>
       <c r="F522" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G522" t="s">
         <v>1803</v>
@@ -19472,7 +19472,7 @@
         <v>1637</v>
       </c>
       <c r="F523" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="G523" t="s">
         <v>1803</v>
@@ -19524,7 +19524,7 @@
         <v>1638</v>
       </c>
       <c r="F525" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G525" t="s">
         <v>1803</v>
@@ -19550,7 +19550,7 @@
         <v>1638</v>
       </c>
       <c r="F526" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G526" t="s">
         <v>1803</v>
@@ -19602,7 +19602,7 @@
         <v>1638</v>
       </c>
       <c r="F528" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G528" t="s">
         <v>1803</v>
@@ -19654,7 +19654,7 @@
         <v>1638</v>
       </c>
       <c r="F530" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G530" t="s">
         <v>1803</v>
@@ -19680,7 +19680,7 @@
         <v>1635</v>
       </c>
       <c r="F531" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G531" t="s">
         <v>1804</v>
@@ -19706,7 +19706,7 @@
         <v>1635</v>
       </c>
       <c r="F532" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G532" t="s">
         <v>1804</v>
@@ -19732,7 +19732,7 @@
         <v>1635</v>
       </c>
       <c r="F533" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G533" t="s">
         <v>1804</v>
@@ -19758,7 +19758,7 @@
         <v>1635</v>
       </c>
       <c r="F534" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G534" t="s">
         <v>1804</v>
@@ -19784,7 +19784,7 @@
         <v>1635</v>
       </c>
       <c r="F535" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G535" t="s">
         <v>1804</v>
@@ -20018,7 +20018,7 @@
         <v>1636</v>
       </c>
       <c r="F544" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G544" t="s">
         <v>1804</v>
@@ -20044,7 +20044,7 @@
         <v>1636</v>
       </c>
       <c r="F545" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G545" t="s">
         <v>1804</v>
@@ -20070,7 +20070,7 @@
         <v>1636</v>
       </c>
       <c r="F546" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G546" t="s">
         <v>1804</v>
@@ -20148,7 +20148,7 @@
         <v>1636</v>
       </c>
       <c r="F549" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G549" t="s">
         <v>1804</v>
@@ -20174,7 +20174,7 @@
         <v>1636</v>
       </c>
       <c r="F550" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G550" t="s">
         <v>1804</v>
@@ -20252,7 +20252,7 @@
         <v>1636</v>
       </c>
       <c r="F553" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G553" t="s">
         <v>1804</v>
@@ -20278,7 +20278,7 @@
         <v>1636</v>
       </c>
       <c r="F554" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G554" t="s">
         <v>1804</v>
@@ -20304,7 +20304,7 @@
         <v>1636</v>
       </c>
       <c r="F555" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G555" t="s">
         <v>1804</v>
@@ -20330,7 +20330,7 @@
         <v>1636</v>
       </c>
       <c r="F556" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G556" t="s">
         <v>1804</v>
@@ -20356,7 +20356,7 @@
         <v>1637</v>
       </c>
       <c r="F557" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G557" t="s">
         <v>1804</v>
@@ -20382,7 +20382,7 @@
         <v>1637</v>
       </c>
       <c r="F558" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G558" t="s">
         <v>1804</v>
@@ -20408,7 +20408,7 @@
         <v>1637</v>
       </c>
       <c r="F559" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G559" t="s">
         <v>1804</v>
@@ -20434,7 +20434,7 @@
         <v>1637</v>
       </c>
       <c r="F560" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G560" t="s">
         <v>1804</v>
@@ -20460,7 +20460,7 @@
         <v>1637</v>
       </c>
       <c r="F561" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G561" t="s">
         <v>1804</v>
@@ -20486,7 +20486,7 @@
         <v>1637</v>
       </c>
       <c r="F562" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G562" t="s">
         <v>1804</v>
@@ -20512,7 +20512,7 @@
         <v>1638</v>
       </c>
       <c r="F563" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G563" t="s">
         <v>1804</v>
@@ -20538,7 +20538,7 @@
         <v>1638</v>
       </c>
       <c r="F564" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G564" t="s">
         <v>1804</v>
@@ -20564,7 +20564,7 @@
         <v>1638</v>
       </c>
       <c r="F565" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G565" t="s">
         <v>1804</v>
@@ -20590,7 +20590,7 @@
         <v>1638</v>
       </c>
       <c r="F566" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="G566" t="s">
         <v>1804</v>
@@ -20980,7 +20980,7 @@
         <v>1637</v>
       </c>
       <c r="F581" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="G581" t="s">
         <v>1805</v>
@@ -21890,7 +21890,7 @@
         <v>1635</v>
       </c>
       <c r="F616" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G616" t="s">
         <v>1807</v>
@@ -21916,7 +21916,7 @@
         <v>1635</v>
       </c>
       <c r="F617" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G617" t="s">
         <v>1807</v>
@@ -21994,7 +21994,7 @@
         <v>1635</v>
       </c>
       <c r="F620" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G620" t="s">
         <v>1807</v>
@@ -22072,7 +22072,7 @@
         <v>1635</v>
       </c>
       <c r="F623" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G623" t="s">
         <v>1807</v>
@@ -22124,7 +22124,7 @@
         <v>1639</v>
       </c>
       <c r="F625" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G625" t="s">
         <v>1807</v>
@@ -22150,7 +22150,7 @@
         <v>1639</v>
       </c>
       <c r="F626" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G626" t="s">
         <v>1807</v>
@@ -22280,7 +22280,7 @@
         <v>1636</v>
       </c>
       <c r="F631" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G631" t="s">
         <v>1807</v>
@@ -22358,7 +22358,7 @@
         <v>1637</v>
       </c>
       <c r="F634" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G634" t="s">
         <v>1807</v>
@@ -22384,7 +22384,7 @@
         <v>1637</v>
       </c>
       <c r="F635" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G635" t="s">
         <v>1807</v>
@@ -22514,7 +22514,7 @@
         <v>1637</v>
       </c>
       <c r="F640" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G640" t="s">
         <v>1807</v>
@@ -22540,7 +22540,7 @@
         <v>1637</v>
       </c>
       <c r="F641" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G641" t="s">
         <v>1807</v>
@@ -22592,7 +22592,7 @@
         <v>1638</v>
       </c>
       <c r="F643" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G643" t="s">
         <v>1807</v>
@@ -22644,7 +22644,7 @@
         <v>1638</v>
       </c>
       <c r="F645" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G645" t="s">
         <v>1807</v>
@@ -22670,7 +22670,7 @@
         <v>1638</v>
       </c>
       <c r="F646" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G646" t="s">
         <v>1807</v>
@@ -22696,7 +22696,7 @@
         <v>1638</v>
       </c>
       <c r="F647" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G647" t="s">
         <v>1807</v>
@@ -22748,7 +22748,7 @@
         <v>1638</v>
       </c>
       <c r="F649" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G649" t="s">
         <v>1807</v>
@@ -22774,7 +22774,7 @@
         <v>1635</v>
       </c>
       <c r="F650" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G650" t="s">
         <v>1808</v>
@@ -22800,7 +22800,7 @@
         <v>1635</v>
       </c>
       <c r="F651" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G651" t="s">
         <v>1808</v>
@@ -22826,7 +22826,7 @@
         <v>1635</v>
       </c>
       <c r="F652" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G652" t="s">
         <v>1808</v>
@@ -22852,7 +22852,7 @@
         <v>1635</v>
       </c>
       <c r="F653" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G653" t="s">
         <v>1808</v>
@@ -22878,7 +22878,7 @@
         <v>1635</v>
       </c>
       <c r="F654" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G654" t="s">
         <v>1808</v>
@@ -22904,7 +22904,7 @@
         <v>1639</v>
       </c>
       <c r="F655" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G655" t="s">
         <v>1808</v>
@@ -22930,7 +22930,7 @@
         <v>1639</v>
       </c>
       <c r="F656" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G656" t="s">
         <v>1808</v>
@@ -22956,7 +22956,7 @@
         <v>1639</v>
       </c>
       <c r="F657" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G657" t="s">
         <v>1808</v>
@@ -22982,7 +22982,7 @@
         <v>1636</v>
       </c>
       <c r="F658" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="G658" t="s">
         <v>1808</v>
@@ -23008,7 +23008,7 @@
         <v>1636</v>
       </c>
       <c r="F659" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G659" t="s">
         <v>1808</v>
@@ -23034,7 +23034,7 @@
         <v>1636</v>
       </c>
       <c r="F660" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G660" t="s">
         <v>1808</v>
@@ -23060,7 +23060,7 @@
         <v>1636</v>
       </c>
       <c r="F661" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G661" t="s">
         <v>1808</v>
@@ -23086,7 +23086,7 @@
         <v>1636</v>
       </c>
       <c r="F662" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G662" t="s">
         <v>1808</v>
@@ -23112,7 +23112,7 @@
         <v>1636</v>
       </c>
       <c r="F663" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="G663" t="s">
         <v>1808</v>
@@ -23138,7 +23138,7 @@
         <v>1637</v>
       </c>
       <c r="F664" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="G664" t="s">
         <v>1808</v>
@@ -23216,7 +23216,7 @@
         <v>1637</v>
       </c>
       <c r="F667" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G667" t="s">
         <v>1808</v>
@@ -23242,7 +23242,7 @@
         <v>1637</v>
       </c>
       <c r="F668" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G668" t="s">
         <v>1808</v>
@@ -23268,7 +23268,7 @@
         <v>1637</v>
       </c>
       <c r="F669" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G669" t="s">
         <v>1808</v>
@@ -23294,7 +23294,7 @@
         <v>1637</v>
       </c>
       <c r="F670" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G670" t="s">
         <v>1808</v>
@@ -23320,7 +23320,7 @@
         <v>1638</v>
       </c>
       <c r="F671" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G671" t="s">
         <v>1808</v>
@@ -23346,7 +23346,7 @@
         <v>1638</v>
       </c>
       <c r="F672" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G672" t="s">
         <v>1808</v>
@@ -23372,7 +23372,7 @@
         <v>1638</v>
       </c>
       <c r="F673" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="G673" t="s">
         <v>1808</v>
@@ -23398,7 +23398,7 @@
         <v>1638</v>
       </c>
       <c r="F674" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G674" t="s">
         <v>1808</v>
@@ -23450,7 +23450,7 @@
         <v>1638</v>
       </c>
       <c r="F676" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G676" t="s">
         <v>1808</v>
@@ -23476,7 +23476,7 @@
         <v>1638</v>
       </c>
       <c r="F677" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G677" t="s">
         <v>1808</v>
@@ -23528,7 +23528,7 @@
         <v>1638</v>
       </c>
       <c r="F679" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G679" t="s">
         <v>1808</v>
@@ -23554,7 +23554,7 @@
         <v>1638</v>
       </c>
       <c r="F680" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G680" t="s">
         <v>1808</v>
@@ -23580,7 +23580,7 @@
         <v>1638</v>
       </c>
       <c r="F681" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G681" t="s">
         <v>1808</v>
@@ -23606,7 +23606,7 @@
         <v>1638</v>
       </c>
       <c r="F682" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G682" t="s">
         <v>1808</v>
@@ -23632,7 +23632,7 @@
         <v>1635</v>
       </c>
       <c r="F683" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G683" t="s">
         <v>1809</v>
@@ -23658,7 +23658,7 @@
         <v>1635</v>
       </c>
       <c r="F684" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G684" t="s">
         <v>1809</v>
@@ -23684,7 +23684,7 @@
         <v>1635</v>
       </c>
       <c r="F685" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="G685" t="s">
         <v>1809</v>
@@ -23710,7 +23710,7 @@
         <v>1635</v>
       </c>
       <c r="F686" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G686" t="s">
         <v>1809</v>
@@ -23736,7 +23736,7 @@
         <v>1635</v>
       </c>
       <c r="F687" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G687" t="s">
         <v>1809</v>
@@ -23762,7 +23762,7 @@
         <v>1635</v>
       </c>
       <c r="F688" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G688" t="s">
         <v>1809</v>
@@ -23788,7 +23788,7 @@
         <v>1635</v>
       </c>
       <c r="F689" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G689" t="s">
         <v>1809</v>
@@ -23814,7 +23814,7 @@
         <v>1639</v>
       </c>
       <c r="F690" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G690" t="s">
         <v>1809</v>
@@ -23840,7 +23840,7 @@
         <v>1639</v>
       </c>
       <c r="F691" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G691" t="s">
         <v>1809</v>
@@ -23866,7 +23866,7 @@
         <v>1639</v>
       </c>
       <c r="F692" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G692" t="s">
         <v>1809</v>
@@ -23892,7 +23892,7 @@
         <v>1636</v>
       </c>
       <c r="F693" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G693" t="s">
         <v>1809</v>
@@ -23918,7 +23918,7 @@
         <v>1636</v>
       </c>
       <c r="F694" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="G694" t="s">
         <v>1809</v>
@@ -23944,7 +23944,7 @@
         <v>1636</v>
       </c>
       <c r="F695" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G695" t="s">
         <v>1809</v>
@@ -23970,7 +23970,7 @@
         <v>1636</v>
       </c>
       <c r="F696" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="G696" t="s">
         <v>1809</v>
@@ -23996,7 +23996,7 @@
         <v>1636</v>
       </c>
       <c r="F697" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="G697" t="s">
         <v>1809</v>
@@ -24007,13 +24007,13 @@
     </row>
     <row r="698" spans="1:8">
       <c r="A698" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B698" t="s">
         <v>959</v>
       </c>
       <c r="C698" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D698" t="s">
         <v>1614</v>
@@ -24048,7 +24048,7 @@
         <v>1636</v>
       </c>
       <c r="F699" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G699" t="s">
         <v>1809</v>
@@ -24074,7 +24074,7 @@
         <v>1636</v>
       </c>
       <c r="F700" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G700" t="s">
         <v>1809</v>
@@ -24126,7 +24126,7 @@
         <v>1637</v>
       </c>
       <c r="F702" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G702" t="s">
         <v>1809</v>
@@ -24152,7 +24152,7 @@
         <v>1637</v>
       </c>
       <c r="F703" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G703" t="s">
         <v>1809</v>
@@ -24178,7 +24178,7 @@
         <v>1637</v>
       </c>
       <c r="F704" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G704" t="s">
         <v>1809</v>
@@ -24204,7 +24204,7 @@
         <v>1637</v>
       </c>
       <c r="F705" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G705" t="s">
         <v>1809</v>
@@ -24282,7 +24282,7 @@
         <v>1638</v>
       </c>
       <c r="F708" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="G708" t="s">
         <v>1809</v>
@@ -24308,7 +24308,7 @@
         <v>1638</v>
       </c>
       <c r="F709" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G709" t="s">
         <v>1809</v>
@@ -24334,7 +24334,7 @@
         <v>1638</v>
       </c>
       <c r="F710" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G710" t="s">
         <v>1809</v>
@@ -24360,7 +24360,7 @@
         <v>1638</v>
       </c>
       <c r="F711" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G711" t="s">
         <v>1809</v>
@@ -24386,7 +24386,7 @@
         <v>1638</v>
       </c>
       <c r="F712" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G712" t="s">
         <v>1809</v>
@@ -24412,7 +24412,7 @@
         <v>1638</v>
       </c>
       <c r="F713" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G713" t="s">
         <v>1809</v>
@@ -24438,7 +24438,7 @@
         <v>1638</v>
       </c>
       <c r="F714" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G714" t="s">
         <v>1809</v>
@@ -24464,7 +24464,7 @@
         <v>1635</v>
       </c>
       <c r="F715" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G715" t="s">
         <v>1810</v>
@@ -24490,7 +24490,7 @@
         <v>1635</v>
       </c>
       <c r="F716" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G716" t="s">
         <v>1810</v>
@@ -24516,7 +24516,7 @@
         <v>1635</v>
       </c>
       <c r="F717" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G717" t="s">
         <v>1810</v>
@@ -24542,7 +24542,7 @@
         <v>1635</v>
       </c>
       <c r="F718" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G718" t="s">
         <v>1810</v>
@@ -24568,7 +24568,7 @@
         <v>1635</v>
       </c>
       <c r="F719" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G719" t="s">
         <v>1810</v>
@@ -24594,7 +24594,7 @@
         <v>1635</v>
       </c>
       <c r="F720" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G720" t="s">
         <v>1810</v>
@@ -24620,7 +24620,7 @@
         <v>1635</v>
       </c>
       <c r="F721" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G721" t="s">
         <v>1810</v>
@@ -24646,7 +24646,7 @@
         <v>1635</v>
       </c>
       <c r="F722" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G722" t="s">
         <v>1810</v>
@@ -24672,7 +24672,7 @@
         <v>1635</v>
       </c>
       <c r="F723" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G723" t="s">
         <v>1810</v>
@@ -24698,7 +24698,7 @@
         <v>1635</v>
       </c>
       <c r="F724" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G724" t="s">
         <v>1810</v>
@@ -24724,7 +24724,7 @@
         <v>1635</v>
       </c>
       <c r="F725" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G725" t="s">
         <v>1810</v>
@@ -24750,7 +24750,7 @@
         <v>1636</v>
       </c>
       <c r="F726" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G726" t="s">
         <v>1810</v>
@@ -24776,7 +24776,7 @@
         <v>1636</v>
       </c>
       <c r="F727" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G727" t="s">
         <v>1810</v>
@@ -24802,7 +24802,7 @@
         <v>1636</v>
       </c>
       <c r="F728" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G728" t="s">
         <v>1810</v>
@@ -24828,7 +24828,7 @@
         <v>1636</v>
       </c>
       <c r="F729" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G729" t="s">
         <v>1810</v>
@@ -24854,7 +24854,7 @@
         <v>1636</v>
       </c>
       <c r="F730" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G730" t="s">
         <v>1810</v>
@@ -24880,7 +24880,7 @@
         <v>1636</v>
       </c>
       <c r="F731" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G731" t="s">
         <v>1810</v>
@@ -24906,7 +24906,7 @@
         <v>1636</v>
       </c>
       <c r="F732" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G732" t="s">
         <v>1810</v>
@@ -24932,7 +24932,7 @@
         <v>1637</v>
       </c>
       <c r="F733" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G733" t="s">
         <v>1810</v>
@@ -24958,7 +24958,7 @@
         <v>1637</v>
       </c>
       <c r="F734" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G734" t="s">
         <v>1810</v>
@@ -24984,7 +24984,7 @@
         <v>1637</v>
       </c>
       <c r="F735" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G735" t="s">
         <v>1810</v>
@@ -25010,7 +25010,7 @@
         <v>1637</v>
       </c>
       <c r="F736" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G736" t="s">
         <v>1810</v>
@@ -25036,7 +25036,7 @@
         <v>1637</v>
       </c>
       <c r="F737" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G737" t="s">
         <v>1810</v>
@@ -25062,7 +25062,7 @@
         <v>1638</v>
       </c>
       <c r="F738" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G738" t="s">
         <v>1810</v>
@@ -25088,7 +25088,7 @@
         <v>1638</v>
       </c>
       <c r="F739" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G739" t="s">
         <v>1810</v>
@@ -25114,7 +25114,7 @@
         <v>1638</v>
       </c>
       <c r="F740" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G740" t="s">
         <v>1810</v>
@@ -25140,7 +25140,7 @@
         <v>1638</v>
       </c>
       <c r="F741" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G741" t="s">
         <v>1810</v>
@@ -25166,7 +25166,7 @@
         <v>1635</v>
       </c>
       <c r="F742" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G742" t="s">
         <v>1811</v>
@@ -25244,7 +25244,7 @@
         <v>1639</v>
       </c>
       <c r="F745" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G745" t="s">
         <v>1811</v>
@@ -25296,7 +25296,7 @@
         <v>1639</v>
       </c>
       <c r="F747" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G747" t="s">
         <v>1811</v>
@@ -25686,7 +25686,7 @@
         <v>1635</v>
       </c>
       <c r="F762" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G762" t="s">
         <v>1812</v>
@@ -25712,7 +25712,7 @@
         <v>1635</v>
       </c>
       <c r="F763" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G763" t="s">
         <v>1812</v>
@@ -25738,7 +25738,7 @@
         <v>1635</v>
       </c>
       <c r="F764" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G764" t="s">
         <v>1812</v>
@@ -25764,7 +25764,7 @@
         <v>1635</v>
       </c>
       <c r="F765" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G765" t="s">
         <v>1812</v>
@@ -25816,7 +25816,7 @@
         <v>1639</v>
       </c>
       <c r="F767" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G767" t="s">
         <v>1812</v>
@@ -25842,7 +25842,7 @@
         <v>1639</v>
       </c>
       <c r="F768" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G768" t="s">
         <v>1812</v>
@@ -25894,7 +25894,7 @@
         <v>1636</v>
       </c>
       <c r="F770" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G770" t="s">
         <v>1812</v>
@@ -25946,7 +25946,7 @@
         <v>1637</v>
       </c>
       <c r="F772" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G772" t="s">
         <v>1812</v>
@@ -26024,7 +26024,7 @@
         <v>1637</v>
       </c>
       <c r="F775" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G775" t="s">
         <v>1812</v>
@@ -26050,7 +26050,7 @@
         <v>1638</v>
       </c>
       <c r="F776" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G776" t="s">
         <v>1812</v>
@@ -26076,7 +26076,7 @@
         <v>1638</v>
       </c>
       <c r="F777" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G777" t="s">
         <v>1812</v>
@@ -26102,7 +26102,7 @@
         <v>1638</v>
       </c>
       <c r="F778" t="s">
-        <v>1747</v>
+        <v>1686</v>
       </c>
       <c r="G778" t="s">
         <v>1812</v>
@@ -26674,7 +26674,7 @@
         <v>1638</v>
       </c>
       <c r="F800" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G800" t="s">
         <v>1813</v>
@@ -26726,7 +26726,7 @@
         <v>1638</v>
       </c>
       <c r="F802" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G802" t="s">
         <v>1813</v>
@@ -26778,7 +26778,7 @@
         <v>1635</v>
       </c>
       <c r="F804" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G804" t="s">
         <v>1814</v>
@@ -26804,7 +26804,7 @@
         <v>1635</v>
       </c>
       <c r="F805" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G805" t="s">
         <v>1814</v>
@@ -26830,7 +26830,7 @@
         <v>1635</v>
       </c>
       <c r="F806" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G806" t="s">
         <v>1814</v>
@@ -26856,7 +26856,7 @@
         <v>1635</v>
       </c>
       <c r="F807" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G807" t="s">
         <v>1814</v>
@@ -26882,7 +26882,7 @@
         <v>1639</v>
       </c>
       <c r="F808" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G808" t="s">
         <v>1814</v>
@@ -26908,7 +26908,7 @@
         <v>1639</v>
       </c>
       <c r="F809" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G809" t="s">
         <v>1814</v>
@@ -26960,7 +26960,7 @@
         <v>1636</v>
       </c>
       <c r="F811" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G811" t="s">
         <v>1814</v>
@@ -27012,7 +27012,7 @@
         <v>1636</v>
       </c>
       <c r="F813" t="s">
-        <v>1747</v>
+        <v>1686</v>
       </c>
       <c r="G813" t="s">
         <v>1814</v>
@@ -27038,7 +27038,7 @@
         <v>1637</v>
       </c>
       <c r="F814" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G814" t="s">
         <v>1814</v>
@@ -27116,7 +27116,7 @@
         <v>1637</v>
       </c>
       <c r="F817" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G817" t="s">
         <v>1814</v>
@@ -27142,7 +27142,7 @@
         <v>1638</v>
       </c>
       <c r="F818" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G818" t="s">
         <v>1814</v>
@@ -27194,7 +27194,7 @@
         <v>1638</v>
       </c>
       <c r="F820" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G820" t="s">
         <v>1814</v>
@@ -27220,7 +27220,7 @@
         <v>1635</v>
       </c>
       <c r="F821" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G821" t="s">
         <v>1815</v>
@@ -27402,7 +27402,7 @@
         <v>1635</v>
       </c>
       <c r="F828" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G828" t="s">
         <v>1815</v>
@@ -27428,7 +27428,7 @@
         <v>1635</v>
       </c>
       <c r="F829" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G829" t="s">
         <v>1815</v>
@@ -27454,7 +27454,7 @@
         <v>1639</v>
       </c>
       <c r="F830" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G830" t="s">
         <v>1815</v>
@@ -27480,7 +27480,7 @@
         <v>1636</v>
       </c>
       <c r="F831" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G831" t="s">
         <v>1815</v>
@@ -27506,7 +27506,7 @@
         <v>1636</v>
       </c>
       <c r="F832" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G832" t="s">
         <v>1815</v>
@@ -27532,7 +27532,7 @@
         <v>1636</v>
       </c>
       <c r="F833" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G833" t="s">
         <v>1815</v>
@@ -27558,7 +27558,7 @@
         <v>1637</v>
       </c>
       <c r="F834" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G834" t="s">
         <v>1815</v>
@@ -27584,7 +27584,7 @@
         <v>1637</v>
       </c>
       <c r="F835" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G835" t="s">
         <v>1815</v>
@@ -27610,7 +27610,7 @@
         <v>1637</v>
       </c>
       <c r="F836" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G836" t="s">
         <v>1815</v>
@@ -27636,7 +27636,7 @@
         <v>1638</v>
       </c>
       <c r="F837" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G837" t="s">
         <v>1815</v>
@@ -27688,7 +27688,7 @@
         <v>1638</v>
       </c>
       <c r="F839" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G839" t="s">
         <v>1815</v>
@@ -27740,7 +27740,7 @@
         <v>1638</v>
       </c>
       <c r="F841" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G841" t="s">
         <v>1815</v>
@@ -27766,7 +27766,7 @@
         <v>1638</v>
       </c>
       <c r="F842" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G842" t="s">
         <v>1815</v>
@@ -27792,7 +27792,7 @@
         <v>1638</v>
       </c>
       <c r="F843" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G843" t="s">
         <v>1815</v>
@@ -27818,7 +27818,7 @@
         <v>1635</v>
       </c>
       <c r="F844" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="G844" t="s">
         <v>1816</v>
@@ -27870,7 +27870,7 @@
         <v>1635</v>
       </c>
       <c r="F846" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="G846" t="s">
         <v>1816</v>
@@ -27974,7 +27974,7 @@
         <v>1635</v>
       </c>
       <c r="F850" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G850" t="s">
         <v>1816</v>
@@ -28000,7 +28000,7 @@
         <v>1635</v>
       </c>
       <c r="F851" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="G851" t="s">
         <v>1816</v>
@@ -28052,7 +28052,7 @@
         <v>1639</v>
       </c>
       <c r="F853" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G853" t="s">
         <v>1816</v>
@@ -28130,7 +28130,7 @@
         <v>1636</v>
       </c>
       <c r="F856" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G856" t="s">
         <v>1816</v>
@@ -28182,7 +28182,7 @@
         <v>1636</v>
       </c>
       <c r="F858" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G858" t="s">
         <v>1816</v>
@@ -28234,7 +28234,7 @@
         <v>1636</v>
       </c>
       <c r="F860" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G860" t="s">
         <v>1816</v>
@@ -28286,7 +28286,7 @@
         <v>1637</v>
       </c>
       <c r="F862" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G862" t="s">
         <v>1816</v>
@@ -28312,7 +28312,7 @@
         <v>1637</v>
       </c>
       <c r="F863" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G863" t="s">
         <v>1816</v>
@@ -28442,7 +28442,7 @@
         <v>1637</v>
       </c>
       <c r="F868" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G868" t="s">
         <v>1816</v>
@@ -28520,7 +28520,7 @@
         <v>1638</v>
       </c>
       <c r="F871" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G871" t="s">
         <v>1816</v>
@@ -28546,7 +28546,7 @@
         <v>1638</v>
       </c>
       <c r="F872" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G872" t="s">
         <v>1816</v>
@@ -28650,7 +28650,7 @@
         <v>1635</v>
       </c>
       <c r="F876" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G876" t="s">
         <v>1817</v>
@@ -28676,7 +28676,7 @@
         <v>1635</v>
       </c>
       <c r="F877" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G877" t="s">
         <v>1817</v>
@@ -28702,7 +28702,7 @@
         <v>1636</v>
       </c>
       <c r="F878" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G878" t="s">
         <v>1817</v>
@@ -28780,7 +28780,7 @@
         <v>1636</v>
       </c>
       <c r="F881" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G881" t="s">
         <v>1817</v>
@@ -28806,7 +28806,7 @@
         <v>1636</v>
       </c>
       <c r="F882" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G882" t="s">
         <v>1817</v>
@@ -28832,7 +28832,7 @@
         <v>1637</v>
       </c>
       <c r="F883" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G883" t="s">
         <v>1817</v>
@@ -28858,7 +28858,7 @@
         <v>1637</v>
       </c>
       <c r="F884" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G884" t="s">
         <v>1817</v>
@@ -28884,7 +28884,7 @@
         <v>1637</v>
       </c>
       <c r="F885" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G885" t="s">
         <v>1817</v>
@@ -28910,7 +28910,7 @@
         <v>1637</v>
       </c>
       <c r="F886" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G886" t="s">
         <v>1817</v>
@@ -28936,7 +28936,7 @@
         <v>1637</v>
       </c>
       <c r="F887" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G887" t="s">
         <v>1817</v>
@@ -28962,7 +28962,7 @@
         <v>1638</v>
       </c>
       <c r="F888" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G888" t="s">
         <v>1817</v>
@@ -29092,7 +29092,7 @@
         <v>1638</v>
       </c>
       <c r="F893" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G893" t="s">
         <v>1817</v>
@@ -29118,7 +29118,7 @@
         <v>1638</v>
       </c>
       <c r="F894" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="G894" t="s">
         <v>1817</v>
@@ -29144,7 +29144,7 @@
         <v>1635</v>
       </c>
       <c r="F895" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G895" t="s">
         <v>1818</v>
@@ -29170,7 +29170,7 @@
         <v>1639</v>
       </c>
       <c r="F896" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G896" t="s">
         <v>1818</v>
@@ -29196,7 +29196,7 @@
         <v>1639</v>
       </c>
       <c r="F897" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G897" t="s">
         <v>1818</v>
@@ -29222,7 +29222,7 @@
         <v>1639</v>
       </c>
       <c r="F898" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G898" t="s">
         <v>1818</v>
@@ -29248,7 +29248,7 @@
         <v>1636</v>
       </c>
       <c r="F899" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G899" t="s">
         <v>1818</v>
@@ -29326,7 +29326,7 @@
         <v>1636</v>
       </c>
       <c r="F902" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G902" t="s">
         <v>1818</v>
@@ -29352,7 +29352,7 @@
         <v>1636</v>
       </c>
       <c r="F903" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G903" t="s">
         <v>1818</v>
@@ -29378,7 +29378,7 @@
         <v>1636</v>
       </c>
       <c r="F904" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G904" t="s">
         <v>1818</v>
@@ -29430,7 +29430,7 @@
         <v>1637</v>
       </c>
       <c r="F906" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G906" t="s">
         <v>1818</v>
@@ -29456,7 +29456,7 @@
         <v>1637</v>
       </c>
       <c r="F907" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G907" t="s">
         <v>1818</v>
@@ -29482,7 +29482,7 @@
         <v>1637</v>
       </c>
       <c r="F908" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G908" t="s">
         <v>1818</v>
@@ -29534,7 +29534,7 @@
         <v>1638</v>
       </c>
       <c r="F910" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G910" t="s">
         <v>1818</v>
@@ -29560,7 +29560,7 @@
         <v>1638</v>
       </c>
       <c r="F911" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G911" t="s">
         <v>1818</v>
@@ -29612,7 +29612,7 @@
         <v>1638</v>
       </c>
       <c r="F913" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G913" t="s">
         <v>1818</v>
@@ -29638,7 +29638,7 @@
         <v>1635</v>
       </c>
       <c r="F914" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G914" t="s">
         <v>1819</v>
@@ -29664,7 +29664,7 @@
         <v>1635</v>
       </c>
       <c r="F915" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G915" t="s">
         <v>1819</v>
@@ -29690,7 +29690,7 @@
         <v>1635</v>
       </c>
       <c r="F916" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G916" t="s">
         <v>1819</v>
@@ -29716,7 +29716,7 @@
         <v>1635</v>
       </c>
       <c r="F917" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G917" t="s">
         <v>1819</v>
@@ -29742,7 +29742,7 @@
         <v>1639</v>
       </c>
       <c r="F918" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G918" t="s">
         <v>1819</v>
@@ -29768,7 +29768,7 @@
         <v>1636</v>
       </c>
       <c r="F919" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G919" t="s">
         <v>1819</v>
@@ -29846,7 +29846,7 @@
         <v>1636</v>
       </c>
       <c r="F922" t="s">
-        <v>1747</v>
+        <v>1686</v>
       </c>
       <c r="G922" t="s">
         <v>1819</v>
@@ -29924,7 +29924,7 @@
         <v>1637</v>
       </c>
       <c r="F925" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G925" t="s">
         <v>1819</v>
@@ -29950,7 +29950,7 @@
         <v>1637</v>
       </c>
       <c r="F926" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G926" t="s">
         <v>1819</v>
@@ -29976,7 +29976,7 @@
         <v>1637</v>
       </c>
       <c r="F927" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G927" t="s">
         <v>1819</v>
@@ -30028,7 +30028,7 @@
         <v>1638</v>
       </c>
       <c r="F929" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G929" t="s">
         <v>1819</v>
@@ -30080,7 +30080,7 @@
         <v>1635</v>
       </c>
       <c r="F931" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G931" t="s">
         <v>1820</v>
@@ -30158,7 +30158,7 @@
         <v>1635</v>
       </c>
       <c r="F934" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G934" t="s">
         <v>1820</v>
@@ -30184,7 +30184,7 @@
         <v>1635</v>
       </c>
       <c r="F935" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G935" t="s">
         <v>1820</v>
@@ -30210,7 +30210,7 @@
         <v>1639</v>
       </c>
       <c r="F936" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G936" t="s">
         <v>1820</v>
@@ -30236,7 +30236,7 @@
         <v>1636</v>
       </c>
       <c r="F937" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G937" t="s">
         <v>1820</v>
@@ -30262,7 +30262,7 @@
         <v>1636</v>
       </c>
       <c r="F938" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G938" t="s">
         <v>1820</v>
@@ -30288,7 +30288,7 @@
         <v>1636</v>
       </c>
       <c r="F939" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G939" t="s">
         <v>1820</v>
@@ -30314,7 +30314,7 @@
         <v>1636</v>
       </c>
       <c r="F940" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G940" t="s">
         <v>1820</v>
@@ -30340,7 +30340,7 @@
         <v>1637</v>
       </c>
       <c r="F941" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G941" t="s">
         <v>1820</v>
@@ -30470,7 +30470,7 @@
         <v>1638</v>
       </c>
       <c r="F946" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G946" t="s">
         <v>1820</v>
@@ -30513,7 +30513,7 @@
         <v>959</v>
       </c>
       <c r="C948" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D948" t="s">
         <v>1613</v>
@@ -30565,7 +30565,7 @@
         <v>959</v>
       </c>
       <c r="C950" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D950" t="s">
         <v>1614</v>
@@ -30600,7 +30600,7 @@
         <v>1638</v>
       </c>
       <c r="F951" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G951" t="s">
         <v>1820</v>
@@ -30626,7 +30626,7 @@
         <v>1638</v>
       </c>
       <c r="F952" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G952" t="s">
         <v>1820</v>
@@ -30652,7 +30652,7 @@
         <v>1635</v>
       </c>
       <c r="F953" t="s">
-        <v>1747</v>
+        <v>1686</v>
       </c>
       <c r="G953" t="s">
         <v>1821</v>
@@ -30678,7 +30678,7 @@
         <v>1635</v>
       </c>
       <c r="F954" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G954" t="s">
         <v>1821</v>
@@ -30704,7 +30704,7 @@
         <v>1635</v>
       </c>
       <c r="F955" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G955" t="s">
         <v>1821</v>
@@ -30730,7 +30730,7 @@
         <v>1635</v>
       </c>
       <c r="F956" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G956" t="s">
         <v>1821</v>
@@ -30756,7 +30756,7 @@
         <v>1635</v>
       </c>
       <c r="F957" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G957" t="s">
         <v>1821</v>
@@ -30782,7 +30782,7 @@
         <v>1639</v>
       </c>
       <c r="F958" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G958" t="s">
         <v>1821</v>
@@ -30808,7 +30808,7 @@
         <v>1636</v>
       </c>
       <c r="F959" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G959" t="s">
         <v>1821</v>
@@ -30886,7 +30886,7 @@
         <v>1636</v>
       </c>
       <c r="F962" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G962" t="s">
         <v>1821</v>
@@ -30964,7 +30964,7 @@
         <v>1637</v>
       </c>
       <c r="F965" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G965" t="s">
         <v>1821</v>
@@ -30990,7 +30990,7 @@
         <v>1637</v>
       </c>
       <c r="F966" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G966" t="s">
         <v>1821</v>
@@ -31016,7 +31016,7 @@
         <v>1637</v>
       </c>
       <c r="F967" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G967" t="s">
         <v>1821</v>
@@ -31042,7 +31042,7 @@
         <v>1638</v>
       </c>
       <c r="F968" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G968" t="s">
         <v>1821</v>
@@ -31120,7 +31120,7 @@
         <v>1635</v>
       </c>
       <c r="F971" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G971" t="s">
         <v>1822</v>
@@ -31172,7 +31172,7 @@
         <v>1635</v>
       </c>
       <c r="F973" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G973" t="s">
         <v>1822</v>
@@ -31302,7 +31302,7 @@
         <v>1636</v>
       </c>
       <c r="F978" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G978" t="s">
         <v>1822</v>
@@ -31328,7 +31328,7 @@
         <v>1636</v>
       </c>
       <c r="F979" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G979" t="s">
         <v>1822</v>
@@ -31666,7 +31666,7 @@
         <v>1635</v>
       </c>
       <c r="F992" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G992" t="s">
         <v>1823</v>
@@ -31744,7 +31744,7 @@
         <v>1635</v>
       </c>
       <c r="F995" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G995" t="s">
         <v>1823</v>
@@ -31770,7 +31770,7 @@
         <v>1639</v>
       </c>
       <c r="F996" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G996" t="s">
         <v>1823</v>
@@ -31796,7 +31796,7 @@
         <v>1639</v>
       </c>
       <c r="F997" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G997" t="s">
         <v>1823</v>
@@ -31822,7 +31822,7 @@
         <v>1639</v>
       </c>
       <c r="F998" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G998" t="s">
         <v>1823</v>
@@ -31848,7 +31848,7 @@
         <v>1636</v>
       </c>
       <c r="F999" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G999" t="s">
         <v>1823</v>
@@ -31978,7 +31978,7 @@
         <v>1636</v>
       </c>
       <c r="F1004" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1004" t="s">
         <v>1823</v>
@@ -32004,7 +32004,7 @@
         <v>1636</v>
       </c>
       <c r="F1005" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1005" t="s">
         <v>1823</v>
@@ -32082,7 +32082,7 @@
         <v>1637</v>
       </c>
       <c r="F1008" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1008" t="s">
         <v>1823</v>
@@ -32108,7 +32108,7 @@
         <v>1637</v>
       </c>
       <c r="F1009" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1009" t="s">
         <v>1823</v>
@@ -32134,7 +32134,7 @@
         <v>1638</v>
       </c>
       <c r="F1010" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1010" t="s">
         <v>1823</v>
@@ -32160,7 +32160,7 @@
         <v>1638</v>
       </c>
       <c r="F1011" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1011" t="s">
         <v>1823</v>
@@ -32186,7 +32186,7 @@
         <v>1638</v>
       </c>
       <c r="F1012" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1012" t="s">
         <v>1823</v>
@@ -32212,7 +32212,7 @@
         <v>1638</v>
       </c>
       <c r="F1013" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G1013" t="s">
         <v>1823</v>
@@ -32940,7 +32940,7 @@
         <v>1639</v>
       </c>
       <c r="F1041" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1041" t="s">
         <v>1825</v>
@@ -32966,7 +32966,7 @@
         <v>1639</v>
       </c>
       <c r="F1042" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1042" t="s">
         <v>1825</v>
@@ -33980,7 +33980,7 @@
         <v>1639</v>
       </c>
       <c r="F1081" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1081" t="s">
         <v>1827</v>
@@ -34006,7 +34006,7 @@
         <v>1639</v>
       </c>
       <c r="F1082" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1082" t="s">
         <v>1827</v>
@@ -34110,7 +34110,7 @@
         <v>1636</v>
       </c>
       <c r="F1086" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1086" t="s">
         <v>1827</v>
@@ -34318,7 +34318,7 @@
         <v>1635</v>
       </c>
       <c r="F1094" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1094" t="s">
         <v>1828</v>
@@ -34344,7 +34344,7 @@
         <v>1635</v>
       </c>
       <c r="F1095" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1095" t="s">
         <v>1828</v>
@@ -34370,7 +34370,7 @@
         <v>1635</v>
       </c>
       <c r="F1096" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1096" t="s">
         <v>1828</v>
@@ -34396,7 +34396,7 @@
         <v>1636</v>
       </c>
       <c r="F1097" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1097" t="s">
         <v>1828</v>
@@ -34422,7 +34422,7 @@
         <v>1636</v>
       </c>
       <c r="F1098" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1098" t="s">
         <v>1828</v>
@@ -34474,7 +34474,7 @@
         <v>1636</v>
       </c>
       <c r="F1100" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1100" t="s">
         <v>1828</v>
@@ -34500,7 +34500,7 @@
         <v>1637</v>
       </c>
       <c r="F1101" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1101" t="s">
         <v>1828</v>
@@ -34578,7 +34578,7 @@
         <v>1637</v>
       </c>
       <c r="F1104" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1104" t="s">
         <v>1828</v>
@@ -34604,7 +34604,7 @@
         <v>1637</v>
       </c>
       <c r="F1105" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1105" t="s">
         <v>1828</v>
@@ -34630,7 +34630,7 @@
         <v>1638</v>
       </c>
       <c r="F1106" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1106" t="s">
         <v>1828</v>
@@ -34760,7 +34760,7 @@
         <v>1638</v>
       </c>
       <c r="F1111" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G1111" t="s">
         <v>1828</v>
@@ -34786,7 +34786,7 @@
         <v>1638</v>
       </c>
       <c r="F1112" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1112" t="s">
         <v>1828</v>
@@ -34994,7 +34994,7 @@
         <v>1636</v>
       </c>
       <c r="F1120" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1120" t="s">
         <v>1829</v>
@@ -35020,7 +35020,7 @@
         <v>1636</v>
       </c>
       <c r="F1121" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1121" t="s">
         <v>1829</v>
@@ -35072,7 +35072,7 @@
         <v>1636</v>
       </c>
       <c r="F1123" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1123" t="s">
         <v>1829</v>
@@ -35124,7 +35124,7 @@
         <v>1637</v>
       </c>
       <c r="F1125" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1125" t="s">
         <v>1829</v>
@@ -35176,7 +35176,7 @@
         <v>1637</v>
       </c>
       <c r="F1127" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1127" t="s">
         <v>1829</v>
@@ -35332,7 +35332,7 @@
         <v>1638</v>
       </c>
       <c r="F1133" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G1133" t="s">
         <v>1829</v>
@@ -35410,7 +35410,7 @@
         <v>1635</v>
       </c>
       <c r="F1136" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="G1136" t="s">
         <v>1830</v>
@@ -35462,7 +35462,7 @@
         <v>1639</v>
       </c>
       <c r="F1138" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1138" t="s">
         <v>1830</v>
@@ -35488,7 +35488,7 @@
         <v>1639</v>
       </c>
       <c r="F1139" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1139" t="s">
         <v>1830</v>
@@ -35540,7 +35540,7 @@
         <v>1636</v>
       </c>
       <c r="F1141" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1141" t="s">
         <v>1830</v>
@@ -35566,7 +35566,7 @@
         <v>1636</v>
       </c>
       <c r="F1142" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1142" t="s">
         <v>1830</v>
@@ -35722,7 +35722,7 @@
         <v>1638</v>
       </c>
       <c r="F1148" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1148" t="s">
         <v>1830</v>
@@ -35748,7 +35748,7 @@
         <v>1638</v>
       </c>
       <c r="F1149" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1149" t="s">
         <v>1830</v>
@@ -35904,7 +35904,7 @@
         <v>1638</v>
       </c>
       <c r="F1155" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1155" t="s">
         <v>1830</v>
@@ -35930,7 +35930,7 @@
         <v>1638</v>
       </c>
       <c r="F1156" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1156" t="s">
         <v>1830</v>
@@ -36086,7 +36086,7 @@
         <v>1639</v>
       </c>
       <c r="F1162" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1162" t="s">
         <v>1831</v>
@@ -36112,7 +36112,7 @@
         <v>1639</v>
       </c>
       <c r="F1163" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1163" t="s">
         <v>1831</v>
@@ -36398,7 +36398,7 @@
         <v>1635</v>
       </c>
       <c r="F1174" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1174" t="s">
         <v>1832</v>
@@ -36528,7 +36528,7 @@
         <v>1635</v>
       </c>
       <c r="F1179" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1179" t="s">
         <v>1832</v>
@@ -36554,7 +36554,7 @@
         <v>1635</v>
       </c>
       <c r="F1180" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1180" t="s">
         <v>1832</v>
@@ -36580,7 +36580,7 @@
         <v>1636</v>
       </c>
       <c r="F1181" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="G1181" t="s">
         <v>1832</v>
@@ -36606,7 +36606,7 @@
         <v>1636</v>
       </c>
       <c r="F1182" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1182" t="s">
         <v>1832</v>
@@ -36632,7 +36632,7 @@
         <v>1636</v>
       </c>
       <c r="F1183" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1183" t="s">
         <v>1832</v>
@@ -36658,7 +36658,7 @@
         <v>1637</v>
       </c>
       <c r="F1184" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1184" t="s">
         <v>1832</v>
@@ -36788,7 +36788,7 @@
         <v>1637</v>
       </c>
       <c r="F1189" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1189" t="s">
         <v>1832</v>
@@ -36814,7 +36814,7 @@
         <v>1637</v>
       </c>
       <c r="F1190" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1190" t="s">
         <v>1832</v>
@@ -36840,7 +36840,7 @@
         <v>1638</v>
       </c>
       <c r="F1191" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1191" t="s">
         <v>1832</v>
@@ -36918,7 +36918,7 @@
         <v>1638</v>
       </c>
       <c r="F1194" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G1194" t="s">
         <v>1832</v>
@@ -36944,7 +36944,7 @@
         <v>1638</v>
       </c>
       <c r="F1195" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="G1195" t="s">
         <v>1832</v>
@@ -36970,7 +36970,7 @@
         <v>1635</v>
       </c>
       <c r="F1196" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="G1196" t="s">
         <v>1833</v>
@@ -36996,7 +36996,7 @@
         <v>1635</v>
       </c>
       <c r="F1197" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="G1197" t="s">
         <v>1833</v>
@@ -37022,7 +37022,7 @@
         <v>1635</v>
       </c>
       <c r="F1198" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="G1198" t="s">
         <v>1833</v>
@@ -37048,7 +37048,7 @@
         <v>1639</v>
       </c>
       <c r="F1199" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1199" t="s">
         <v>1833</v>
@@ -37074,7 +37074,7 @@
         <v>1639</v>
       </c>
       <c r="F1200" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1200" t="s">
         <v>1833</v>
@@ -37100,7 +37100,7 @@
         <v>1636</v>
       </c>
       <c r="F1201" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1201" t="s">
         <v>1833</v>
@@ -37152,7 +37152,7 @@
         <v>1636</v>
       </c>
       <c r="F1203" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1203" t="s">
         <v>1833</v>
@@ -37204,7 +37204,7 @@
         <v>1637</v>
       </c>
       <c r="F1205" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1205" t="s">
         <v>1833</v>
@@ -37282,7 +37282,7 @@
         <v>1637</v>
       </c>
       <c r="F1208" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1208" t="s">
         <v>1833</v>
@@ -37516,7 +37516,7 @@
         <v>1639</v>
       </c>
       <c r="F1217" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1217" t="s">
         <v>1834</v>
@@ -37646,7 +37646,7 @@
         <v>1637</v>
       </c>
       <c r="F1222" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G1222" t="s">
         <v>1834</v>
@@ -37672,7 +37672,7 @@
         <v>1637</v>
       </c>
       <c r="F1223" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G1223" t="s">
         <v>1834</v>
@@ -37698,7 +37698,7 @@
         <v>1637</v>
       </c>
       <c r="F1224" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G1224" t="s">
         <v>1834</v>
@@ -37724,7 +37724,7 @@
         <v>1637</v>
       </c>
       <c r="F1225" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G1225" t="s">
         <v>1834</v>
@@ -37828,7 +37828,7 @@
         <v>1638</v>
       </c>
       <c r="F1229" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1229" t="s">
         <v>1834</v>
@@ -37854,7 +37854,7 @@
         <v>1638</v>
       </c>
       <c r="F1230" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G1230" t="s">
         <v>1834</v>
@@ -37880,7 +37880,7 @@
         <v>1638</v>
       </c>
       <c r="F1231" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1231" t="s">
         <v>1834</v>
@@ -37906,7 +37906,7 @@
         <v>1638</v>
       </c>
       <c r="F1232" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G1232" t="s">
         <v>1834</v>
@@ -37984,7 +37984,7 @@
         <v>1635</v>
       </c>
       <c r="F1235" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1235" t="s">
         <v>1835</v>
@@ -38010,7 +38010,7 @@
         <v>1635</v>
       </c>
       <c r="F1236" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1236" t="s">
         <v>1835</v>
@@ -38036,7 +38036,7 @@
         <v>1635</v>
       </c>
       <c r="F1237" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1237" t="s">
         <v>1835</v>
@@ -38062,7 +38062,7 @@
         <v>1639</v>
       </c>
       <c r="F1238" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1238" t="s">
         <v>1835</v>
@@ -38088,7 +38088,7 @@
         <v>1639</v>
       </c>
       <c r="F1239" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1239" t="s">
         <v>1835</v>
@@ -38114,7 +38114,7 @@
         <v>1639</v>
       </c>
       <c r="F1240" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1240" t="s">
         <v>1835</v>
@@ -38140,7 +38140,7 @@
         <v>1639</v>
       </c>
       <c r="F1241" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1241" t="s">
         <v>1835</v>
@@ -38166,7 +38166,7 @@
         <v>1636</v>
       </c>
       <c r="F1242" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G1242" t="s">
         <v>1835</v>
@@ -38192,7 +38192,7 @@
         <v>1636</v>
       </c>
       <c r="F1243" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G1243" t="s">
         <v>1835</v>
@@ -38218,7 +38218,7 @@
         <v>1636</v>
       </c>
       <c r="F1244" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G1244" t="s">
         <v>1835</v>
@@ -38244,7 +38244,7 @@
         <v>1636</v>
       </c>
       <c r="F1245" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G1245" t="s">
         <v>1835</v>
@@ -38270,7 +38270,7 @@
         <v>1636</v>
       </c>
       <c r="F1246" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1246" t="s">
         <v>1835</v>
@@ -38296,7 +38296,7 @@
         <v>1636</v>
       </c>
       <c r="F1247" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1247" t="s">
         <v>1835</v>
@@ -38322,7 +38322,7 @@
         <v>1637</v>
       </c>
       <c r="F1248" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1248" t="s">
         <v>1835</v>
@@ -38348,7 +38348,7 @@
         <v>1637</v>
       </c>
       <c r="F1249" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1249" t="s">
         <v>1835</v>
@@ -38374,7 +38374,7 @@
         <v>1637</v>
       </c>
       <c r="F1250" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1250" t="s">
         <v>1835</v>
@@ -38400,7 +38400,7 @@
         <v>1638</v>
       </c>
       <c r="F1251" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1251" t="s">
         <v>1835</v>
@@ -38426,7 +38426,7 @@
         <v>1638</v>
       </c>
       <c r="F1252" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G1252" t="s">
         <v>1835</v>
@@ -38452,7 +38452,7 @@
         <v>1638</v>
       </c>
       <c r="F1253" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="G1253" t="s">
         <v>1835</v>
@@ -38478,7 +38478,7 @@
         <v>1638</v>
       </c>
       <c r="F1254" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G1254" t="s">
         <v>1835</v>
@@ -38504,7 +38504,7 @@
         <v>1638</v>
       </c>
       <c r="F1255" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1255" t="s">
         <v>1835</v>
@@ -38530,7 +38530,7 @@
         <v>1638</v>
       </c>
       <c r="F1256" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G1256" t="s">
         <v>1835</v>
@@ -38556,7 +38556,7 @@
         <v>1635</v>
       </c>
       <c r="F1257" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1257" t="s">
         <v>1836</v>
@@ -38582,7 +38582,7 @@
         <v>1635</v>
       </c>
       <c r="F1258" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1258" t="s">
         <v>1836</v>
@@ -38608,7 +38608,7 @@
         <v>1635</v>
       </c>
       <c r="F1259" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1259" t="s">
         <v>1836</v>
@@ -38634,7 +38634,7 @@
         <v>1635</v>
       </c>
       <c r="F1260" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1260" t="s">
         <v>1836</v>
@@ -38660,7 +38660,7 @@
         <v>1635</v>
       </c>
       <c r="F1261" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1261" t="s">
         <v>1836</v>
@@ -38686,7 +38686,7 @@
         <v>1635</v>
       </c>
       <c r="F1262" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1262" t="s">
         <v>1836</v>
@@ -38738,7 +38738,7 @@
         <v>1635</v>
       </c>
       <c r="F1264" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1264" t="s">
         <v>1836</v>
@@ -38764,7 +38764,7 @@
         <v>1635</v>
       </c>
       <c r="F1265" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1265" t="s">
         <v>1836</v>
@@ -38790,7 +38790,7 @@
         <v>1635</v>
       </c>
       <c r="F1266" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1266" t="s">
         <v>1836</v>
@@ -38816,7 +38816,7 @@
         <v>1635</v>
       </c>
       <c r="F1267" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1267" t="s">
         <v>1836</v>
@@ -38842,7 +38842,7 @@
         <v>1635</v>
       </c>
       <c r="F1268" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1268" t="s">
         <v>1836</v>
@@ -38868,7 +38868,7 @@
         <v>1635</v>
       </c>
       <c r="F1269" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1269" t="s">
         <v>1836</v>
@@ -38920,7 +38920,7 @@
         <v>1635</v>
       </c>
       <c r="F1271" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1271" t="s">
         <v>1836</v>
@@ -38946,7 +38946,7 @@
         <v>1635</v>
       </c>
       <c r="F1272" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1272" t="s">
         <v>1836</v>
@@ -38972,7 +38972,7 @@
         <v>1635</v>
       </c>
       <c r="F1273" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1273" t="s">
         <v>1836</v>
@@ -39024,7 +39024,7 @@
         <v>1635</v>
       </c>
       <c r="F1275" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1275" t="s">
         <v>1836</v>
@@ -39050,7 +39050,7 @@
         <v>1635</v>
       </c>
       <c r="F1276" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1276" t="s">
         <v>1836</v>
@@ -39128,7 +39128,7 @@
         <v>1635</v>
       </c>
       <c r="F1279" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1279" t="s">
         <v>1836</v>
@@ -39154,7 +39154,7 @@
         <v>1635</v>
       </c>
       <c r="F1280" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1280" t="s">
         <v>1836</v>
@@ -39180,7 +39180,7 @@
         <v>1635</v>
       </c>
       <c r="F1281" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1281" t="s">
         <v>1836</v>
@@ -39206,7 +39206,7 @@
         <v>1635</v>
       </c>
       <c r="F1282" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1282" t="s">
         <v>1836</v>
@@ -39284,7 +39284,7 @@
         <v>1639</v>
       </c>
       <c r="F1285" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1285" t="s">
         <v>1836</v>
@@ -39310,7 +39310,7 @@
         <v>1639</v>
       </c>
       <c r="F1286" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1286" t="s">
         <v>1836</v>
@@ -39336,7 +39336,7 @@
         <v>1639</v>
       </c>
       <c r="F1287" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1287" t="s">
         <v>1836</v>
@@ -39414,7 +39414,7 @@
         <v>1639</v>
       </c>
       <c r="F1290" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1290" t="s">
         <v>1836</v>
@@ -39440,7 +39440,7 @@
         <v>1639</v>
       </c>
       <c r="F1291" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1291" t="s">
         <v>1836</v>
@@ -39466,7 +39466,7 @@
         <v>1639</v>
       </c>
       <c r="F1292" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1292" t="s">
         <v>1836</v>
@@ -39596,7 +39596,7 @@
         <v>1636</v>
       </c>
       <c r="F1297" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1297" t="s">
         <v>1836</v>
@@ -39622,7 +39622,7 @@
         <v>1636</v>
       </c>
       <c r="F1298" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1298" t="s">
         <v>1836</v>
@@ -39700,7 +39700,7 @@
         <v>1636</v>
       </c>
       <c r="F1301" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1301" t="s">
         <v>1836</v>
@@ -39726,7 +39726,7 @@
         <v>1636</v>
       </c>
       <c r="F1302" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1302" t="s">
         <v>1836</v>
@@ -39778,7 +39778,7 @@
         <v>1636</v>
       </c>
       <c r="F1304" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1304" t="s">
         <v>1836</v>
@@ -39856,7 +39856,7 @@
         <v>1636</v>
       </c>
       <c r="F1307" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1307" t="s">
         <v>1836</v>
@@ -39882,7 +39882,7 @@
         <v>1636</v>
       </c>
       <c r="F1308" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1308" t="s">
         <v>1836</v>
@@ -39960,7 +39960,7 @@
         <v>1636</v>
       </c>
       <c r="F1311" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1311" t="s">
         <v>1836</v>
@@ -40012,7 +40012,7 @@
         <v>1636</v>
       </c>
       <c r="F1313" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1313" t="s">
         <v>1836</v>
@@ -40038,7 +40038,7 @@
         <v>1636</v>
       </c>
       <c r="F1314" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1314" t="s">
         <v>1836</v>
@@ -40142,7 +40142,7 @@
         <v>1636</v>
       </c>
       <c r="F1318" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1318" t="s">
         <v>1836</v>
@@ -40168,7 +40168,7 @@
         <v>1636</v>
       </c>
       <c r="F1319" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1319" t="s">
         <v>1836</v>
@@ -40272,7 +40272,7 @@
         <v>1637</v>
       </c>
       <c r="F1323" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1323" t="s">
         <v>1836</v>
@@ -40376,7 +40376,7 @@
         <v>1637</v>
       </c>
       <c r="F1327" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1327" t="s">
         <v>1836</v>
@@ -40402,7 +40402,7 @@
         <v>1637</v>
       </c>
       <c r="F1328" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1328" t="s">
         <v>1836</v>
@@ -40454,7 +40454,7 @@
         <v>1637</v>
       </c>
       <c r="F1330" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G1330" t="s">
         <v>1836</v>
@@ -40480,7 +40480,7 @@
         <v>1637</v>
       </c>
       <c r="F1331" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1331" t="s">
         <v>1836</v>
@@ -40506,7 +40506,7 @@
         <v>1637</v>
       </c>
       <c r="F1332" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1332" t="s">
         <v>1836</v>
@@ -40610,7 +40610,7 @@
         <v>1637</v>
       </c>
       <c r="F1336" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1336" t="s">
         <v>1836</v>
@@ -40636,7 +40636,7 @@
         <v>1637</v>
       </c>
       <c r="F1337" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1337" t="s">
         <v>1836</v>
@@ -40792,7 +40792,7 @@
         <v>1637</v>
       </c>
       <c r="F1343" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1343" t="s">
         <v>1836</v>
@@ -40818,7 +40818,7 @@
         <v>1637</v>
       </c>
       <c r="F1344" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1344" t="s">
         <v>1836</v>
@@ -40896,7 +40896,7 @@
         <v>1638</v>
       </c>
       <c r="F1347" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1347" t="s">
         <v>1836</v>
@@ -41000,7 +41000,7 @@
         <v>1638</v>
       </c>
       <c r="F1351" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1351" t="s">
         <v>1836</v>
@@ -41104,7 +41104,7 @@
         <v>1638</v>
       </c>
       <c r="F1355" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1355" t="s">
         <v>1836</v>
@@ -41130,7 +41130,7 @@
         <v>1638</v>
       </c>
       <c r="F1356" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1356" t="s">
         <v>1836</v>
@@ -41182,7 +41182,7 @@
         <v>1638</v>
       </c>
       <c r="F1358" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1358" t="s">
         <v>1836</v>
@@ -41208,7 +41208,7 @@
         <v>1638</v>
       </c>
       <c r="F1359" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1359" t="s">
         <v>1836</v>
@@ -41260,7 +41260,7 @@
         <v>1635</v>
       </c>
       <c r="F1361" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1361" t="s">
         <v>1837</v>
@@ -41286,7 +41286,7 @@
         <v>1635</v>
       </c>
       <c r="F1362" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G1362" t="s">
         <v>1837</v>
@@ -41390,7 +41390,7 @@
         <v>1635</v>
       </c>
       <c r="F1366" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1366" t="s">
         <v>1837</v>
@@ -41520,7 +41520,7 @@
         <v>1635</v>
       </c>
       <c r="F1371" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1371" t="s">
         <v>1837</v>
@@ -41598,7 +41598,7 @@
         <v>1635</v>
       </c>
       <c r="F1374" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1374" t="s">
         <v>1837</v>
@@ -41650,7 +41650,7 @@
         <v>1635</v>
       </c>
       <c r="F1376" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G1376" t="s">
         <v>1837</v>
@@ -41676,7 +41676,7 @@
         <v>1635</v>
       </c>
       <c r="F1377" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1377" t="s">
         <v>1837</v>
@@ -41832,7 +41832,7 @@
         <v>1639</v>
       </c>
       <c r="F1383" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1383" t="s">
         <v>1837</v>
@@ -41910,7 +41910,7 @@
         <v>1639</v>
       </c>
       <c r="F1386" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1386" t="s">
         <v>1837</v>
@@ -42040,7 +42040,7 @@
         <v>1639</v>
       </c>
       <c r="F1391" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1391" t="s">
         <v>1837</v>
@@ -42118,7 +42118,7 @@
         <v>1639</v>
       </c>
       <c r="F1394" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1394" t="s">
         <v>1837</v>
@@ -42170,7 +42170,7 @@
         <v>1636</v>
       </c>
       <c r="F1396" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="G1396" t="s">
         <v>1837</v>
@@ -42248,7 +42248,7 @@
         <v>1636</v>
       </c>
       <c r="F1399" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="G1399" t="s">
         <v>1837</v>
@@ -42300,7 +42300,7 @@
         <v>1636</v>
       </c>
       <c r="F1401" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1401" t="s">
         <v>1837</v>
@@ -42326,7 +42326,7 @@
         <v>1636</v>
       </c>
       <c r="F1402" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1402" t="s">
         <v>1837</v>
@@ -42352,7 +42352,7 @@
         <v>1636</v>
       </c>
       <c r="F1403" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1403" t="s">
         <v>1837</v>
@@ -42430,7 +42430,7 @@
         <v>1636</v>
       </c>
       <c r="F1406" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1406" t="s">
         <v>1837</v>
@@ -42456,7 +42456,7 @@
         <v>1636</v>
       </c>
       <c r="F1407" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1407" t="s">
         <v>1837</v>
@@ -42508,7 +42508,7 @@
         <v>1636</v>
       </c>
       <c r="F1409" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G1409" t="s">
         <v>1837</v>
@@ -42560,7 +42560,7 @@
         <v>1636</v>
       </c>
       <c r="F1411" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1411" t="s">
         <v>1837</v>
@@ -42586,7 +42586,7 @@
         <v>1636</v>
       </c>
       <c r="F1412" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1412" t="s">
         <v>1837</v>
@@ -42664,7 +42664,7 @@
         <v>1637</v>
       </c>
       <c r="F1415" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1415" t="s">
         <v>1837</v>
@@ -42690,7 +42690,7 @@
         <v>1637</v>
       </c>
       <c r="F1416" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1416" t="s">
         <v>1837</v>
@@ -42716,7 +42716,7 @@
         <v>1637</v>
       </c>
       <c r="F1417" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G1417" t="s">
         <v>1837</v>
@@ -42794,7 +42794,7 @@
         <v>1637</v>
       </c>
       <c r="F1420" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G1420" t="s">
         <v>1837</v>
@@ -42820,7 +42820,7 @@
         <v>1637</v>
       </c>
       <c r="F1421" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1421" t="s">
         <v>1837</v>
@@ -42924,7 +42924,7 @@
         <v>1637</v>
       </c>
       <c r="F1425" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="G1425" t="s">
         <v>1837</v>
@@ -42976,7 +42976,7 @@
         <v>1637</v>
       </c>
       <c r="F1427" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G1427" t="s">
         <v>1837</v>
@@ -43080,7 +43080,7 @@
         <v>1638</v>
       </c>
       <c r="F1431" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="G1431" t="s">
         <v>1837</v>
@@ -43444,7 +43444,7 @@
         <v>1635</v>
       </c>
       <c r="F1445" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G1445" t="s">
         <v>1838</v>
@@ -43470,7 +43470,7 @@
         <v>1635</v>
       </c>
       <c r="F1446" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1446" t="s">
         <v>1838</v>
@@ -43496,7 +43496,7 @@
         <v>1635</v>
       </c>
       <c r="F1447" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1447" t="s">
         <v>1838</v>
@@ -43548,7 +43548,7 @@
         <v>1635</v>
       </c>
       <c r="F1449" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1449" t="s">
         <v>1838</v>
@@ -43574,7 +43574,7 @@
         <v>1635</v>
       </c>
       <c r="F1450" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1450" t="s">
         <v>1838</v>
@@ -43600,7 +43600,7 @@
         <v>1639</v>
       </c>
       <c r="F1451" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1451" t="s">
         <v>1838</v>
@@ -43652,7 +43652,7 @@
         <v>1639</v>
       </c>
       <c r="F1453" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1453" t="s">
         <v>1838</v>
@@ -43678,7 +43678,7 @@
         <v>1639</v>
       </c>
       <c r="F1454" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1454" t="s">
         <v>1838</v>
@@ -43704,7 +43704,7 @@
         <v>1639</v>
       </c>
       <c r="F1455" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1455" t="s">
         <v>1838</v>
@@ -43730,7 +43730,7 @@
         <v>1639</v>
       </c>
       <c r="F1456" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1456" t="s">
         <v>1838</v>
@@ -43808,7 +43808,7 @@
         <v>1636</v>
       </c>
       <c r="F1459" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1459" t="s">
         <v>1838</v>
@@ -43834,7 +43834,7 @@
         <v>1636</v>
       </c>
       <c r="F1460" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G1460" t="s">
         <v>1838</v>
@@ -43860,7 +43860,7 @@
         <v>1636</v>
       </c>
       <c r="F1461" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1461" t="s">
         <v>1838</v>
@@ -43886,7 +43886,7 @@
         <v>1636</v>
       </c>
       <c r="F1462" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G1462" t="s">
         <v>1838</v>
@@ -43964,7 +43964,7 @@
         <v>1636</v>
       </c>
       <c r="F1465" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G1465" t="s">
         <v>1838</v>
@@ -43990,7 +43990,7 @@
         <v>1636</v>
       </c>
       <c r="F1466" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="G1466" t="s">
         <v>1838</v>
@@ -44016,7 +44016,7 @@
         <v>1636</v>
       </c>
       <c r="F1467" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1467" t="s">
         <v>1838</v>
@@ -44042,7 +44042,7 @@
         <v>1637</v>
       </c>
       <c r="F1468" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1468" t="s">
         <v>1838</v>
@@ -44068,7 +44068,7 @@
         <v>1637</v>
       </c>
       <c r="F1469" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1469" t="s">
         <v>1838</v>
@@ -44094,7 +44094,7 @@
         <v>1637</v>
       </c>
       <c r="F1470" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1470" t="s">
         <v>1838</v>
@@ -44120,7 +44120,7 @@
         <v>1637</v>
       </c>
       <c r="F1471" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1471" t="s">
         <v>1838</v>
@@ -44160,7 +44160,7 @@
         <v>891</v>
       </c>
       <c r="B1473" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C1473" t="s">
         <v>1589</v>
@@ -44186,7 +44186,7 @@
         <v>892</v>
       </c>
       <c r="B1474" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C1474" t="s">
         <v>1590</v>
@@ -44198,7 +44198,7 @@
         <v>1637</v>
       </c>
       <c r="F1474" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="G1474" t="s">
         <v>1838</v>
@@ -44250,7 +44250,7 @@
         <v>1637</v>
       </c>
       <c r="F1476" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="G1476" t="s">
         <v>1838</v>
@@ -44276,7 +44276,7 @@
         <v>1637</v>
       </c>
       <c r="F1477" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1477" t="s">
         <v>1838</v>
@@ -44302,7 +44302,7 @@
         <v>1637</v>
       </c>
       <c r="F1478" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G1478" t="s">
         <v>1838</v>
@@ -44328,7 +44328,7 @@
         <v>1637</v>
       </c>
       <c r="F1479" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1479" t="s">
         <v>1838</v>
@@ -44354,7 +44354,7 @@
         <v>1637</v>
       </c>
       <c r="F1480" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1480" t="s">
         <v>1838</v>
@@ -44380,7 +44380,7 @@
         <v>1637</v>
       </c>
       <c r="F1481" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1481" t="s">
         <v>1838</v>
@@ -44406,7 +44406,7 @@
         <v>1637</v>
       </c>
       <c r="F1482" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1482" t="s">
         <v>1838</v>
@@ -44432,7 +44432,7 @@
         <v>1637</v>
       </c>
       <c r="F1483" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1483" t="s">
         <v>1838</v>
@@ -44458,7 +44458,7 @@
         <v>1637</v>
       </c>
       <c r="F1484" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1484" t="s">
         <v>1838</v>
@@ -44510,7 +44510,7 @@
         <v>1637</v>
       </c>
       <c r="F1486" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1486" t="s">
         <v>1838</v>
@@ -44536,7 +44536,7 @@
         <v>1637</v>
       </c>
       <c r="F1487" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1487" t="s">
         <v>1838</v>
@@ -44562,7 +44562,7 @@
         <v>1637</v>
       </c>
       <c r="F1488" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1488" t="s">
         <v>1838</v>
@@ -44588,7 +44588,7 @@
         <v>1638</v>
       </c>
       <c r="F1489" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G1489" t="s">
         <v>1838</v>
@@ -44614,7 +44614,7 @@
         <v>1638</v>
       </c>
       <c r="F1490" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1490" t="s">
         <v>1838</v>
@@ -44666,7 +44666,7 @@
         <v>1638</v>
       </c>
       <c r="F1492" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1492" t="s">
         <v>1838</v>
@@ -44692,7 +44692,7 @@
         <v>1638</v>
       </c>
       <c r="F1493" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1493" t="s">
         <v>1838</v>
@@ -44718,7 +44718,7 @@
         <v>1638</v>
       </c>
       <c r="F1494" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1494" t="s">
         <v>1838</v>
@@ -44770,7 +44770,7 @@
         <v>1638</v>
       </c>
       <c r="F1496" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1496" t="s">
         <v>1838</v>
@@ -44796,7 +44796,7 @@
         <v>1638</v>
       </c>
       <c r="F1497" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1497" t="s">
         <v>1838</v>
@@ -44822,7 +44822,7 @@
         <v>1638</v>
       </c>
       <c r="F1498" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1498" t="s">
         <v>1838</v>
@@ -44848,7 +44848,7 @@
         <v>1638</v>
       </c>
       <c r="F1499" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1499" t="s">
         <v>1838</v>
@@ -44874,7 +44874,7 @@
         <v>1638</v>
       </c>
       <c r="F1500" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="G1500" t="s">
         <v>1838</v>
@@ -44900,7 +44900,7 @@
         <v>1638</v>
       </c>
       <c r="F1501" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="G1501" t="s">
         <v>1838</v>
@@ -44926,7 +44926,7 @@
         <v>1638</v>
       </c>
       <c r="F1502" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1502" t="s">
         <v>1838</v>
@@ -44952,7 +44952,7 @@
         <v>1638</v>
       </c>
       <c r="F1503" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1503" t="s">
         <v>1838</v>
@@ -45004,7 +45004,7 @@
         <v>1635</v>
       </c>
       <c r="F1505" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1505" t="s">
         <v>1839</v>
@@ -45134,7 +45134,7 @@
         <v>1635</v>
       </c>
       <c r="F1510" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1510" t="s">
         <v>1839</v>
@@ -45160,7 +45160,7 @@
         <v>1635</v>
       </c>
       <c r="F1511" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1511" t="s">
         <v>1839</v>
@@ -45186,7 +45186,7 @@
         <v>1635</v>
       </c>
       <c r="F1512" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1512" t="s">
         <v>1839</v>
@@ -45238,7 +45238,7 @@
         <v>1639</v>
       </c>
       <c r="F1514" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1514" t="s">
         <v>1839</v>
@@ -45264,7 +45264,7 @@
         <v>1639</v>
       </c>
       <c r="F1515" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1515" t="s">
         <v>1839</v>
@@ -45290,7 +45290,7 @@
         <v>1639</v>
       </c>
       <c r="F1516" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1516" t="s">
         <v>1839</v>
@@ -45316,7 +45316,7 @@
         <v>1639</v>
       </c>
       <c r="F1517" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1517" t="s">
         <v>1839</v>
@@ -45342,7 +45342,7 @@
         <v>1639</v>
       </c>
       <c r="F1518" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="G1518" t="s">
         <v>1839</v>
@@ -45368,7 +45368,7 @@
         <v>1639</v>
       </c>
       <c r="F1519" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1519" t="s">
         <v>1839</v>
@@ -45394,7 +45394,7 @@
         <v>1636</v>
       </c>
       <c r="F1520" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1520" t="s">
         <v>1839</v>
@@ -45446,7 +45446,7 @@
         <v>1636</v>
       </c>
       <c r="F1522" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1522" t="s">
         <v>1839</v>
@@ -45576,7 +45576,7 @@
         <v>1636</v>
       </c>
       <c r="F1527" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1527" t="s">
         <v>1839</v>
@@ -45628,7 +45628,7 @@
         <v>1637</v>
       </c>
       <c r="F1529" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1529" t="s">
         <v>1839</v>
@@ -45654,7 +45654,7 @@
         <v>1637</v>
       </c>
       <c r="F1530" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1530" t="s">
         <v>1839</v>
@@ -45784,7 +45784,7 @@
         <v>1637</v>
       </c>
       <c r="F1535" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1535" t="s">
         <v>1839</v>
@@ -45810,7 +45810,7 @@
         <v>1637</v>
       </c>
       <c r="F1536" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1536" t="s">
         <v>1839</v>
@@ -45836,7 +45836,7 @@
         <v>1638</v>
       </c>
       <c r="F1537" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1537" t="s">
         <v>1839</v>
@@ -45914,7 +45914,7 @@
         <v>1638</v>
       </c>
       <c r="F1540" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1540" t="s">
         <v>1839</v>
@@ -45940,7 +45940,7 @@
         <v>1638</v>
       </c>
       <c r="F1541" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1541" t="s">
         <v>1839</v>
@@ -45966,7 +45966,7 @@
         <v>1638</v>
       </c>
       <c r="F1542" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1542" t="s">
         <v>1839</v>
@@ -46018,7 +46018,7 @@
         <v>1638</v>
       </c>
       <c r="F1544" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="G1544" t="s">
         <v>1839</v>
@@ -46096,7 +46096,7 @@
         <v>1638</v>
       </c>
       <c r="F1547" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1547" t="s">
         <v>1839</v>
@@ -46200,7 +46200,7 @@
         <v>1638</v>
       </c>
       <c r="F1551" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="G1551" t="s">
         <v>1839</v>
@@ -46226,7 +46226,7 @@
         <v>1638</v>
       </c>
       <c r="F1552" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G1552" t="s">
         <v>1839</v>
@@ -46252,7 +46252,7 @@
         <v>1638</v>
       </c>
       <c r="F1553" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="G1553" t="s">
         <v>1839</v>
@@ -46356,7 +46356,7 @@
         <v>1635</v>
       </c>
       <c r="F1557" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="G1557" t="s">
         <v>1840</v>
@@ -46382,7 +46382,7 @@
         <v>1635</v>
       </c>
       <c r="F1558" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1558" t="s">
         <v>1840</v>
@@ -46408,7 +46408,7 @@
         <v>1635</v>
       </c>
       <c r="F1559" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="G1559" t="s">
         <v>1840</v>
@@ -46434,7 +46434,7 @@
         <v>1635</v>
       </c>
       <c r="F1560" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G1560" t="s">
         <v>1840</v>
@@ -46460,7 +46460,7 @@
         <v>1635</v>
       </c>
       <c r="F1561" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1561" t="s">
         <v>1840</v>
@@ -46538,7 +46538,7 @@
         <v>1635</v>
       </c>
       <c r="F1564" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1564" t="s">
         <v>1840</v>
@@ -46564,7 +46564,7 @@
         <v>1635</v>
       </c>
       <c r="F1565" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1565" t="s">
         <v>1840</v>
@@ -46590,7 +46590,7 @@
         <v>1635</v>
       </c>
       <c r="F1566" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1566" t="s">
         <v>1840</v>
@@ -46668,7 +46668,7 @@
         <v>1635</v>
       </c>
       <c r="F1569" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1569" t="s">
         <v>1840</v>
@@ -46694,7 +46694,7 @@
         <v>1635</v>
       </c>
       <c r="F1570" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G1570" t="s">
         <v>1840</v>
@@ -46720,7 +46720,7 @@
         <v>1639</v>
       </c>
       <c r="F1571" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1571" t="s">
         <v>1840</v>
@@ -46746,7 +46746,7 @@
         <v>1639</v>
       </c>
       <c r="F1572" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1572" t="s">
         <v>1840</v>
@@ -46772,7 +46772,7 @@
         <v>1639</v>
       </c>
       <c r="F1573" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G1573" t="s">
         <v>1840</v>
@@ -46798,7 +46798,7 @@
         <v>1636</v>
       </c>
       <c r="F1574" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1574" t="s">
         <v>1840</v>
@@ -46824,7 +46824,7 @@
         <v>1636</v>
       </c>
       <c r="F1575" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G1575" t="s">
         <v>1840</v>
@@ -46850,7 +46850,7 @@
         <v>1636</v>
       </c>
       <c r="F1576" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G1576" t="s">
         <v>1840</v>
@@ -46876,7 +46876,7 @@
         <v>1636</v>
       </c>
       <c r="F1577" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G1577" t="s">
         <v>1840</v>
@@ -46902,7 +46902,7 @@
         <v>1636</v>
       </c>
       <c r="F1578" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G1578" t="s">
         <v>1840</v>
@@ -46928,7 +46928,7 @@
         <v>1636</v>
       </c>
       <c r="F1579" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G1579" t="s">
         <v>1840</v>
@@ -46954,7 +46954,7 @@
         <v>1636</v>
       </c>
       <c r="F1580" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1580" t="s">
         <v>1840</v>
@@ -46980,7 +46980,7 @@
         <v>1636</v>
       </c>
       <c r="F1581" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G1581" t="s">
         <v>1840</v>
@@ -47006,7 +47006,7 @@
         <v>1637</v>
       </c>
       <c r="F1582" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1582" t="s">
         <v>1840</v>
@@ -47032,7 +47032,7 @@
         <v>1637</v>
       </c>
       <c r="F1583" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1583" t="s">
         <v>1840</v>
@@ -47058,7 +47058,7 @@
         <v>1637</v>
       </c>
       <c r="F1584" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G1584" t="s">
         <v>1840</v>
@@ -47084,7 +47084,7 @@
         <v>1637</v>
       </c>
       <c r="F1585" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1585" t="s">
         <v>1840</v>
@@ -47110,7 +47110,7 @@
         <v>1637</v>
       </c>
       <c r="F1586" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1586" t="s">
         <v>1840</v>
@@ -47136,7 +47136,7 @@
         <v>1637</v>
       </c>
       <c r="F1587" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G1587" t="s">
         <v>1840</v>
@@ -47162,7 +47162,7 @@
         <v>1637</v>
       </c>
       <c r="F1588" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G1588" t="s">
         <v>1840</v>
@@ -47188,7 +47188,7 @@
         <v>1637</v>
       </c>
       <c r="F1589" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G1589" t="s">
         <v>1840</v>
@@ -47214,7 +47214,7 @@
         <v>1637</v>
       </c>
       <c r="F1590" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G1590" t="s">
         <v>1840</v>
@@ -47240,7 +47240,7 @@
         <v>1637</v>
       </c>
       <c r="F1591" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G1591" t="s">
         <v>1840</v>
@@ -47266,7 +47266,7 @@
         <v>1637</v>
       </c>
       <c r="F1592" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G1592" t="s">
         <v>1840</v>
@@ -47292,7 +47292,7 @@
         <v>1637</v>
       </c>
       <c r="F1593" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1593" t="s">
         <v>1840</v>
@@ -47318,7 +47318,7 @@
         <v>1637</v>
       </c>
       <c r="F1594" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1594" t="s">
         <v>1840</v>
@@ -47370,7 +47370,7 @@
         <v>1638</v>
       </c>
       <c r="F1596" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G1596" t="s">
         <v>1840</v>
@@ -47396,7 +47396,7 @@
         <v>1638</v>
       </c>
       <c r="F1597" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="G1597" t="s">
         <v>1840</v>
@@ -47422,7 +47422,7 @@
         <v>1638</v>
       </c>
       <c r="F1598" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G1598" t="s">
         <v>1840</v>

--- a/EDT_Edition.xlsx
+++ b/EDT_Edition.xlsx
@@ -13460,7 +13460,7 @@
         <v>1637</v>
       </c>
       <c r="F292" t="s">
-        <v>1679</v>
+        <v>1669</v>
       </c>
       <c r="G292" t="s">
         <v>1795</v>
@@ -25888,7 +25888,7 @@
         <v>1635</v>
       </c>
       <c r="F770" t="s">
-        <v>1669</v>
+        <v>1640</v>
       </c>
       <c r="G770" t="s">
         <v>1810</v>
@@ -30854,7 +30854,7 @@
         <v>1635</v>
       </c>
       <c r="F961" t="s">
-        <v>1669</v>
+        <v>1640</v>
       </c>
       <c r="G961" t="s">
         <v>1819</v>
@@ -36288,7 +36288,7 @@
         <v>1637</v>
       </c>
       <c r="F1170" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G1170" t="s">
         <v>1829</v>

--- a/EDT_Edition.xlsx
+++ b/EDT_Edition.xlsx
@@ -1246,16 +1246,16 @@
     <t>Cours-EAD-Logiciels de Simulation</t>
   </si>
   <si>
+    <t>TD-Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Systèmes Asservis-SG12</t>
+  </si>
+  <si>
+    <t>TD-Théorie du champ électromagnétique-G1</t>
+  </si>
+  <si>
     <t>TD-Théorie du champ électromagnétique-G2</t>
-  </si>
-  <si>
-    <t>TD-Réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>TP-Systèmes Asservis-SG12</t>
-  </si>
-  <si>
-    <t>TD-Théorie du champ électromagnétique-G1</t>
   </si>
   <si>
     <t>Cours-Capteurs et Métrologie</t>
@@ -11039,7 +11039,7 @@
         <v>1304</v>
       </c>
       <c r="D199" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="E199" t="s">
         <v>1639</v>
@@ -11065,7 +11065,7 @@
         <v>1304</v>
       </c>
       <c r="D200" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E200" t="s">
         <v>1639</v>
@@ -22190,16 +22190,16 @@
         <v>964</v>
       </c>
       <c r="C628" t="s">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="D628" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="E628" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="F628" t="s">
-        <v>1691</v>
+        <v>1681</v>
       </c>
       <c r="G628" t="s">
         <v>1806</v>
@@ -22210,13 +22210,13 @@
     </row>
     <row r="629" spans="1:8">
       <c r="A629" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="B629" t="s">
         <v>964</v>
       </c>
       <c r="C629" t="s">
-        <v>1346</v>
+        <v>1331</v>
       </c>
       <c r="D629" t="s">
         <v>1612</v>
@@ -22225,7 +22225,7 @@
         <v>1636</v>
       </c>
       <c r="F629" t="s">
-        <v>1681</v>
+        <v>1644</v>
       </c>
       <c r="G629" t="s">
         <v>1806</v>
@@ -22236,22 +22236,22 @@
     </row>
     <row r="630" spans="1:8">
       <c r="A630" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="B630" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C630" t="s">
-        <v>1331</v>
+        <v>1416</v>
       </c>
       <c r="D630" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="E630" t="s">
         <v>1636</v>
       </c>
       <c r="F630" t="s">
-        <v>1644</v>
+        <v>1671</v>
       </c>
       <c r="G630" t="s">
         <v>1806</v>
@@ -22265,19 +22265,19 @@
         <v>412</v>
       </c>
       <c r="B631" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C631" t="s">
-        <v>1416</v>
+        <v>1305</v>
       </c>
       <c r="D631" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="E631" t="s">
         <v>1636</v>
       </c>
       <c r="F631" t="s">
-        <v>1671</v>
+        <v>1646</v>
       </c>
       <c r="G631" t="s">
         <v>1806</v>
@@ -22294,16 +22294,16 @@
         <v>964</v>
       </c>
       <c r="C632" t="s">
-        <v>1305</v>
+        <v>1332</v>
       </c>
       <c r="D632" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E632" t="s">
         <v>1636</v>
       </c>
       <c r="F632" t="s">
-        <v>1646</v>
+        <v>1691</v>
       </c>
       <c r="G632" t="s">
         <v>1806</v>
@@ -45272,7 +45272,7 @@
     </row>
     <row r="1516" spans="1:8">
       <c r="A1516" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B1516" t="s">
         <v>964</v>
@@ -45402,7 +45402,7 @@
     </row>
     <row r="1521" spans="1:8">
       <c r="A1521" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B1521" t="s">
         <v>964</v>
@@ -46078,7 +46078,7 @@
     </row>
     <row r="1547" spans="1:8">
       <c r="A1547" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B1547" t="s">
         <v>962</v>
